--- a/research/traditional_assets/database/data/croatia/croatia_machinery.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_machinery.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0805</v>
+        <v>-0.0432</v>
       </c>
       <c r="G2">
-        <v>-0.09061876247504989</v>
+        <v>-0.1768807339449541</v>
       </c>
       <c r="H2">
-        <v>-0.09061876247504989</v>
+        <v>-0.1768807339449541</v>
       </c>
       <c r="I2">
-        <v>-0.2275449101796407</v>
+        <v>-0.06752293577981652</v>
       </c>
       <c r="J2">
-        <v>-0.2275449101796407</v>
+        <v>-0.06752293577981652</v>
       </c>
       <c r="K2">
-        <v>-13.5</v>
+        <v>-6.26</v>
       </c>
       <c r="L2">
-        <v>-0.2694610778443114</v>
+        <v>-0.1148623853211009</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.05</v>
+        <v>0.694</v>
       </c>
       <c r="V2">
-        <v>1.558641975308642</v>
+        <v>0.3242990654205607</v>
       </c>
       <c r="W2">
-        <v>0.5421686746987953</v>
+        <v>0.1580808080808081</v>
       </c>
       <c r="X2">
-        <v>1.492128916761022</v>
+        <v>0.7939954300249978</v>
       </c>
       <c r="Y2">
-        <v>-0.9499602420622266</v>
+        <v>-0.6359146219441898</v>
       </c>
       <c r="Z2">
-        <v>1.171107994389902</v>
+        <v>1.727416798732171</v>
       </c>
       <c r="AA2">
-        <v>-0.2664796633941094</v>
+        <v>-0.1166402535657686</v>
       </c>
       <c r="AB2">
-        <v>0.1019732939395655</v>
+        <v>0.1857349359608882</v>
       </c>
       <c r="AC2">
-        <v>-0.3684529573336748</v>
+        <v>-0.3023751895266568</v>
       </c>
       <c r="AD2">
-        <v>76.2</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>76.2</v>
+        <v>17.5</v>
       </c>
       <c r="AG2">
-        <v>71.15000000000001</v>
+        <v>16.806</v>
       </c>
       <c r="AH2">
-        <v>0.9592145015105741</v>
+        <v>0.8910386965376782</v>
       </c>
       <c r="AI2">
-        <v>2.093406593406593</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AJ2">
-        <v>0.9564457588385537</v>
+        <v>0.8870473978676238</v>
       </c>
       <c r="AK2">
-        <v>2.269537480063796</v>
+        <v>-2.05101293629485</v>
       </c>
       <c r="AL2">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AM2">
-        <v>2.957</v>
+        <v>2.305</v>
       </c>
       <c r="AN2">
-        <v>-9.060642092746731</v>
+        <v>-15.21739130434783</v>
       </c>
       <c r="AO2">
-        <v>-3.8</v>
+        <v>-1.586206896551724</v>
       </c>
       <c r="AP2">
-        <v>-8.460166468489893</v>
+        <v>-14.61391304347826</v>
       </c>
       <c r="AQ2">
-        <v>-3.855258708150152</v>
+        <v>-1.596529284164859</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0805</v>
+        <v>-0.0432</v>
       </c>
       <c r="G3">
-        <v>-0.09061876247504989</v>
+        <v>-0.1768807339449541</v>
       </c>
       <c r="H3">
-        <v>-0.09061876247504989</v>
+        <v>-0.1768807339449541</v>
       </c>
       <c r="I3">
-        <v>-0.2275449101796407</v>
+        <v>-0.06752293577981652</v>
       </c>
       <c r="J3">
-        <v>-0.2275449101796407</v>
+        <v>-0.06752293577981652</v>
       </c>
       <c r="K3">
-        <v>-13.5</v>
+        <v>-6.26</v>
       </c>
       <c r="L3">
-        <v>-0.2694610778443114</v>
+        <v>-0.1148623853211009</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.05</v>
+        <v>0.694</v>
       </c>
       <c r="V3">
-        <v>1.558641975308642</v>
+        <v>0.3242990654205607</v>
       </c>
       <c r="W3">
-        <v>0.5421686746987953</v>
+        <v>0.1580808080808081</v>
       </c>
       <c r="X3">
-        <v>1.492128916761022</v>
+        <v>0.7939954300249978</v>
       </c>
       <c r="Y3">
-        <v>-0.9499602420622266</v>
+        <v>-0.6359146219441898</v>
       </c>
       <c r="Z3">
-        <v>1.171107994389902</v>
+        <v>1.727416798732171</v>
       </c>
       <c r="AA3">
-        <v>-0.2664796633941094</v>
+        <v>-0.1166402535657686</v>
       </c>
       <c r="AB3">
-        <v>0.1019732939395655</v>
+        <v>0.1857349359608882</v>
       </c>
       <c r="AC3">
-        <v>-0.3684529573336748</v>
+        <v>-0.3023751895266568</v>
       </c>
       <c r="AD3">
-        <v>76.2</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>76.2</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
-        <v>71.15000000000001</v>
+        <v>16.806</v>
       </c>
       <c r="AH3">
-        <v>0.9592145015105741</v>
+        <v>0.8910386965376782</v>
       </c>
       <c r="AI3">
-        <v>2.093406593406593</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AJ3">
-        <v>0.9564457588385537</v>
+        <v>0.8870473978676238</v>
       </c>
       <c r="AK3">
-        <v>2.269537480063796</v>
+        <v>-2.05101293629485</v>
       </c>
       <c r="AL3">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="AM3">
-        <v>2.957</v>
+        <v>2.305</v>
       </c>
       <c r="AN3">
-        <v>-9.060642092746731</v>
+        <v>-15.21739130434783</v>
       </c>
       <c r="AO3">
-        <v>-3.8</v>
+        <v>-1.586206896551724</v>
       </c>
       <c r="AP3">
-        <v>-8.460166468489893</v>
+        <v>-14.61391304347826</v>
       </c>
       <c r="AQ3">
-        <v>-3.855258708150152</v>
+        <v>-1.596529284164859</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/croatia/croatia_machinery.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_machinery.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="zgse_ddjh" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0432</v>
+        <v>0.0576</v>
       </c>
       <c r="G2">
-        <v>-0.1768807339449541</v>
+        <v>0.02443064182194617</v>
       </c>
       <c r="H2">
-        <v>-0.1768807339449541</v>
+        <v>0.02443064182194617</v>
       </c>
       <c r="I2">
-        <v>-0.06752293577981652</v>
+        <v>0.04109730848861284</v>
       </c>
       <c r="J2">
-        <v>-0.06752293577981652</v>
+        <v>0.04062659041781816</v>
       </c>
       <c r="K2">
-        <v>-6.26</v>
+        <v>2.21</v>
       </c>
       <c r="L2">
-        <v>-0.1148623853211009</v>
+        <v>0.02287784679089027</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.694</v>
+        <v>3.78</v>
       </c>
       <c r="V2">
-        <v>0.3242990654205607</v>
+        <v>0.4833759590792838</v>
       </c>
       <c r="W2">
-        <v>0.1580808080808081</v>
+        <v>-0.05092165898617512</v>
       </c>
       <c r="X2">
-        <v>0.7939954300249978</v>
+        <v>0.261277245864561</v>
       </c>
       <c r="Y2">
-        <v>-0.6359146219441898</v>
+        <v>-0.3121989048507361</v>
       </c>
       <c r="Z2">
-        <v>1.727416798732171</v>
+        <v>3.571164510166358</v>
       </c>
       <c r="AA2">
-        <v>-0.1166402535657686</v>
+        <v>0.1450842378691768</v>
       </c>
       <c r="AB2">
-        <v>0.1857349359608882</v>
+        <v>0.1425370712767569</v>
       </c>
       <c r="AC2">
-        <v>-0.3023751895266568</v>
+        <v>0.002547166592419881</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="AG2">
-        <v>16.806</v>
+        <v>14.52</v>
       </c>
       <c r="AH2">
-        <v>0.8910386965376782</v>
+        <v>0.7006125574272588</v>
       </c>
       <c r="AI2">
-        <v>-2.333333333333333</v>
+        <v>0.2946859903381643</v>
       </c>
       <c r="AJ2">
-        <v>0.8870473978676238</v>
+        <v>0.6499552372426141</v>
       </c>
       <c r="AK2">
-        <v>-2.05101293629485</v>
+        <v>0.2489711934156379</v>
       </c>
       <c r="AL2">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AM2">
-        <v>2.305</v>
+        <v>2.375</v>
       </c>
       <c r="AN2">
-        <v>-15.21739130434783</v>
+        <v>4.159090909090909</v>
       </c>
       <c r="AO2">
-        <v>-1.586206896551724</v>
+        <v>1.654166666666667</v>
       </c>
       <c r="AP2">
-        <v>-14.61391304347826</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2">
-        <v>-1.596529284164859</v>
+        <v>1.671578947368421</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0432</v>
+        <v>0.0576</v>
       </c>
       <c r="G3">
-        <v>-0.1768807339449541</v>
+        <v>0.02443064182194617</v>
       </c>
       <c r="H3">
-        <v>-0.1768807339449541</v>
+        <v>0.02443064182194617</v>
       </c>
       <c r="I3">
-        <v>-0.06752293577981652</v>
+        <v>0.04109730848861284</v>
       </c>
       <c r="J3">
-        <v>-0.06752293577981652</v>
+        <v>0.04062659041781816</v>
       </c>
       <c r="K3">
-        <v>-6.26</v>
+        <v>2.21</v>
       </c>
       <c r="L3">
-        <v>-0.1148623853211009</v>
+        <v>0.02287784679089027</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.694</v>
+        <v>3.78</v>
       </c>
       <c r="V3">
-        <v>0.3242990654205607</v>
+        <v>0.4833759590792838</v>
       </c>
       <c r="W3">
-        <v>0.1580808080808081</v>
+        <v>-0.05092165898617512</v>
       </c>
       <c r="X3">
-        <v>0.7939954300249978</v>
+        <v>0.261277245864561</v>
       </c>
       <c r="Y3">
-        <v>-0.6359146219441898</v>
+        <v>-0.3121989048507361</v>
       </c>
       <c r="Z3">
-        <v>1.727416798732171</v>
+        <v>3.571164510166358</v>
       </c>
       <c r="AA3">
-        <v>-0.1166402535657686</v>
+        <v>0.1450842378691768</v>
       </c>
       <c r="AB3">
-        <v>0.1857349359608882</v>
+        <v>0.1425370712767569</v>
       </c>
       <c r="AC3">
-        <v>-0.3023751895266568</v>
+        <v>0.002547166592419881</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="AG3">
-        <v>16.806</v>
+        <v>14.52</v>
       </c>
       <c r="AH3">
-        <v>0.8910386965376782</v>
+        <v>0.7006125574272588</v>
       </c>
       <c r="AI3">
-        <v>-2.333333333333333</v>
+        <v>0.2946859903381643</v>
       </c>
       <c r="AJ3">
-        <v>0.8870473978676238</v>
+        <v>0.6499552372426141</v>
       </c>
       <c r="AK3">
-        <v>-2.05101293629485</v>
+        <v>0.2489711934156379</v>
       </c>
       <c r="AL3">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AM3">
-        <v>2.305</v>
+        <v>2.375</v>
       </c>
       <c r="AN3">
-        <v>-15.21739130434783</v>
+        <v>4.159090909090909</v>
       </c>
       <c r="AO3">
-        <v>-1.586206896551724</v>
+        <v>1.654166666666667</v>
       </c>
       <c r="AP3">
-        <v>-14.61391304347826</v>
+        <v>3.3</v>
       </c>
       <c r="AQ3">
-        <v>-1.596529284164859</v>
+        <v>1.671578947368421</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ðuro Ðakovic Grupa d.d. (ZGSE:DDJH)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ZGSE:DDJH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="F2">
+        <v>4.5804490004901</v>
+      </c>
+      <c r="G2">
+        <v>4.15909090909091</v>
+      </c>
+      <c r="H2">
+        <v>3.08690909090909</v>
+      </c>
+      <c r="I2">
+        <v>0.700612557427259</v>
+      </c>
+      <c r="J2">
+        <v>0.52</v>
+      </c>
+      <c r="K2">
+        <v>7.82</v>
+      </c>
+      <c r="L2">
+        <v>23.0173494575843</v>
+      </c>
+      <c r="M2">
+        <v>22.34</v>
+      </c>
+      <c r="N2">
+        <v>32.8197494575843</v>
+      </c>
+      <c r="O2">
+        <v>18.3</v>
+      </c>
+      <c r="P2">
+        <v>13.5824</v>
+      </c>
+      <c r="Q2">
+        <v>0.142537071276757</v>
+      </c>
+      <c r="R2">
+        <v>0.109412549170061</v>
+      </c>
+      <c r="S2">
+        <v>0.0917967343763948</v>
+      </c>
+      <c r="T2">
+        <v>0.041738</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.261277245864561</v>
+      </c>
+      <c r="X2">
+        <v>0.182726644104293</v>
+      </c>
+      <c r="Y2">
+        <v>3.01269684571996</v>
+      </c>
+      <c r="Z2">
+        <v>1.94899637948608</v>
+      </c>
+      <c r="AA2">
+        <v>18.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.1119472370443838</v>
+      </c>
+      <c r="AC2">
+        <v>0.7083333333333335</v>
+      </c>
+      <c r="AD2">
+        <v>18.3</v>
+      </c>
+      <c r="AE2">
+        <v>2.4</v>
+      </c>
+      <c r="AF2">
+        <v>2.7</v>
+      </c>
+      <c r="AG2">
+        <v>4.4</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>7.82</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.18</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>3.069999999999999</v>
+      </c>
+      <c r="AR2">
+        <v>2.4</v>
+      </c>
+      <c r="AS2">
+        <v>18.3</v>
+      </c>
+      <c r="AT2">
+        <v>3.78</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1150188759599083</v>
+      </c>
+      <c r="C2">
+        <v>34.18567238936672</v>
+      </c>
+      <c r="D2">
+        <v>30.40567238936672</v>
+      </c>
+      <c r="E2">
+        <v>-18.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.78</v>
+      </c>
+      <c r="H2">
+        <v>7.82</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K2">
+        <v>2.7</v>
+      </c>
+      <c r="L2">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="O2">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="P2">
+        <v>2.596666666666667</v>
+      </c>
+      <c r="Q2">
+        <v>5.296666666666667</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1150188759599083</v>
+      </c>
+      <c r="T2">
+        <v>1.032125178898191</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.18</v>
+      </c>
+      <c r="W2">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1148602219831804</v>
+      </c>
+      <c r="C3">
+        <v>33.98789556529071</v>
+      </c>
+      <c r="D3">
+        <v>30.46909556529071</v>
+      </c>
+      <c r="E3">
+        <v>-18.0388</v>
+      </c>
+      <c r="F3">
+        <v>0.2612</v>
+      </c>
+      <c r="G3">
+        <v>3.78</v>
+      </c>
+      <c r="H3">
+        <v>7.82</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K3">
+        <v>2.7</v>
+      </c>
+      <c r="L3">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.01167564</v>
+      </c>
+      <c r="N3">
+        <v>3.154991026666667</v>
+      </c>
+      <c r="O3">
+        <v>0.5678983848</v>
+      </c>
+      <c r="P3">
+        <v>2.587092641866667</v>
+      </c>
+      <c r="Q3">
+        <v>5.287092641866668</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1156501838213944</v>
+      </c>
+      <c r="T3">
+        <v>1.040674094521388</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.18</v>
+      </c>
+      <c r="W3">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>271.2199645301386</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1147015680064526</v>
+      </c>
+      <c r="C4">
+        <v>33.79038388301193</v>
+      </c>
+      <c r="D4">
+        <v>30.53278388301193</v>
+      </c>
+      <c r="E4">
+        <v>-17.7776</v>
+      </c>
+      <c r="F4">
+        <v>0.5224</v>
+      </c>
+      <c r="G4">
+        <v>3.78</v>
+      </c>
+      <c r="H4">
+        <v>7.82</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K4">
+        <v>2.7</v>
+      </c>
+      <c r="L4">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.02335128</v>
+      </c>
+      <c r="N4">
+        <v>3.143315386666667</v>
+      </c>
+      <c r="O4">
+        <v>0.5657967696</v>
+      </c>
+      <c r="P4">
+        <v>2.577518617066667</v>
+      </c>
+      <c r="Q4">
+        <v>5.277518617066667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1162943755167884</v>
+      </c>
+      <c r="T4">
+        <v>1.049397477810365</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.18</v>
+      </c>
+      <c r="W4">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>135.6099822650693</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1145429140297248</v>
+      </c>
+      <c r="C5">
+        <v>33.59313900865854</v>
+      </c>
+      <c r="D5">
+        <v>30.59673900865854</v>
+      </c>
+      <c r="E5">
+        <v>-17.5164</v>
+      </c>
+      <c r="F5">
+        <v>0.7836</v>
+      </c>
+      <c r="G5">
+        <v>3.78</v>
+      </c>
+      <c r="H5">
+        <v>7.82</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K5">
+        <v>2.7</v>
+      </c>
+      <c r="L5">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.03502692</v>
+      </c>
+      <c r="N5">
+        <v>3.131639746666667</v>
+      </c>
+      <c r="O5">
+        <v>0.5636951544000001</v>
+      </c>
+      <c r="P5">
+        <v>2.567944592266667</v>
+      </c>
+      <c r="Q5">
+        <v>5.267944592266668</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1169518495151802</v>
+      </c>
+      <c r="T5">
+        <v>1.05830072467231</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.18</v>
+      </c>
+      <c r="W5">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>90.40665484337951</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1143842600529969</v>
+      </c>
+      <c r="C6">
+        <v>33.39616262234773</v>
+      </c>
+      <c r="D6">
+        <v>30.66096262234774</v>
+      </c>
+      <c r="E6">
+        <v>-17.2552</v>
+      </c>
+      <c r="F6">
+        <v>1.0448</v>
+      </c>
+      <c r="G6">
+        <v>3.78</v>
+      </c>
+      <c r="H6">
+        <v>7.82</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K6">
+        <v>2.7</v>
+      </c>
+      <c r="L6">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M6">
+        <v>0.04670256</v>
+      </c>
+      <c r="N6">
+        <v>3.119964106666667</v>
+      </c>
+      <c r="O6">
+        <v>0.5615935392</v>
+      </c>
+      <c r="P6">
+        <v>2.558370567466667</v>
+      </c>
+      <c r="Q6">
+        <v>5.258370567466667</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1176230208885385</v>
+      </c>
+      <c r="T6">
+        <v>1.067389455843879</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.18</v>
+      </c>
+      <c r="W6">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>67.80499113253464</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1142256060762691</v>
+      </c>
+      <c r="C7">
+        <v>33.19945641833288</v>
+      </c>
+      <c r="D7">
+        <v>30.72545641833288</v>
+      </c>
+      <c r="E7">
+        <v>-16.994</v>
+      </c>
+      <c r="F7">
+        <v>1.306</v>
+      </c>
+      <c r="G7">
+        <v>3.78</v>
+      </c>
+      <c r="H7">
+        <v>7.82</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K7">
+        <v>2.7</v>
+      </c>
+      <c r="L7">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M7">
+        <v>0.05837820000000001</v>
+      </c>
+      <c r="N7">
+        <v>3.108288466666667</v>
+      </c>
+      <c r="O7">
+        <v>0.559491924</v>
+      </c>
+      <c r="P7">
+        <v>2.548796542666667</v>
+      </c>
+      <c r="Q7">
+        <v>5.248796542666668</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1183083221855464</v>
+      </c>
+      <c r="T7">
+        <v>1.076669528724323</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.18</v>
+      </c>
+      <c r="W7">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>54.24399290602771</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1140669520995413</v>
+      </c>
+      <c r="C8">
+        <v>33.0030221051525</v>
+      </c>
+      <c r="D8">
+        <v>30.7902221051525</v>
+      </c>
+      <c r="E8">
+        <v>-16.7328</v>
+      </c>
+      <c r="F8">
+        <v>1.5672</v>
+      </c>
+      <c r="G8">
+        <v>3.78</v>
+      </c>
+      <c r="H8">
+        <v>7.82</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K8">
+        <v>2.7</v>
+      </c>
+      <c r="L8">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M8">
+        <v>0.07005384000000001</v>
+      </c>
+      <c r="N8">
+        <v>3.096612826666667</v>
+      </c>
+      <c r="O8">
+        <v>0.5573903088000001</v>
+      </c>
+      <c r="P8">
+        <v>2.539222517866667</v>
+      </c>
+      <c r="Q8">
+        <v>5.239222517866667</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1190082043612141</v>
+      </c>
+      <c r="T8">
+        <v>1.086147049963926</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.18</v>
+      </c>
+      <c r="W8">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>45.20332742168976</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1139082981228134</v>
+      </c>
+      <c r="C9">
+        <v>32.80686140578114</v>
+      </c>
+      <c r="D9">
+        <v>30.85526140578115</v>
+      </c>
+      <c r="E9">
+        <v>-16.4716</v>
+      </c>
+      <c r="F9">
+        <v>1.8284</v>
+      </c>
+      <c r="G9">
+        <v>3.78</v>
+      </c>
+      <c r="H9">
+        <v>7.82</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K9">
+        <v>2.7</v>
+      </c>
+      <c r="L9">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M9">
+        <v>0.08172948000000002</v>
+      </c>
+      <c r="N9">
+        <v>3.084937186666667</v>
+      </c>
+      <c r="O9">
+        <v>0.5552886936</v>
+      </c>
+      <c r="P9">
+        <v>2.529648493066667</v>
+      </c>
+      <c r="Q9">
+        <v>5.229648493066668</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1197231377664661</v>
+      </c>
+      <c r="T9">
+        <v>1.095828388864595</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.18</v>
+      </c>
+      <c r="W9">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>38.74570921859122</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1137496441460856</v>
+      </c>
+      <c r="C10">
+        <v>32.61097605778219</v>
+      </c>
+      <c r="D10">
+        <v>30.92057605778219</v>
+      </c>
+      <c r="E10">
+        <v>-16.2104</v>
+      </c>
+      <c r="F10">
+        <v>2.0896</v>
+      </c>
+      <c r="G10">
+        <v>3.78</v>
+      </c>
+      <c r="H10">
+        <v>7.82</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K10">
+        <v>2.7</v>
+      </c>
+      <c r="L10">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M10">
+        <v>0.09340512000000001</v>
+      </c>
+      <c r="N10">
+        <v>3.073261546666667</v>
+      </c>
+      <c r="O10">
+        <v>0.5531870784</v>
+      </c>
+      <c r="P10">
+        <v>2.520074468266667</v>
+      </c>
+      <c r="Q10">
+        <v>5.220074468266667</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.120453613202267</v>
+      </c>
+      <c r="T10">
+        <v>1.10572019165441</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.18</v>
+      </c>
+      <c r="W10">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>33.90249556626732</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1135909901693578</v>
+      </c>
+      <c r="C11">
+        <v>32.41536781346257</v>
+      </c>
+      <c r="D11">
+        <v>30.98616781346258</v>
+      </c>
+      <c r="E11">
+        <v>-15.9492</v>
+      </c>
+      <c r="F11">
+        <v>2.3508</v>
+      </c>
+      <c r="G11">
+        <v>3.78</v>
+      </c>
+      <c r="H11">
+        <v>7.82</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K11">
+        <v>2.7</v>
+      </c>
+      <c r="L11">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M11">
+        <v>0.10508076</v>
+      </c>
+      <c r="N11">
+        <v>3.061585906666667</v>
+      </c>
+      <c r="O11">
+        <v>0.5510854632000001</v>
+      </c>
+      <c r="P11">
+        <v>2.510500443466667</v>
+      </c>
+      <c r="Q11">
+        <v>5.210500443466668</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1212001430432503</v>
+      </c>
+      <c r="T11">
+        <v>1.115829396703341</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.18</v>
+      </c>
+      <c r="W11">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>30.13555161445984</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1134323361926299</v>
+      </c>
+      <c r="C12">
+        <v>32.2200384400295</v>
+      </c>
+      <c r="D12">
+        <v>31.0520384400295</v>
+      </c>
+      <c r="E12">
+        <v>-15.688</v>
+      </c>
+      <c r="F12">
+        <v>2.612</v>
+      </c>
+      <c r="G12">
+        <v>3.78</v>
+      </c>
+      <c r="H12">
+        <v>7.82</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K12">
+        <v>2.7</v>
+      </c>
+      <c r="L12">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M12">
+        <v>0.1167564</v>
+      </c>
+      <c r="N12">
+        <v>3.049910266666667</v>
+      </c>
+      <c r="O12">
+        <v>0.5489838480000001</v>
+      </c>
+      <c r="P12">
+        <v>2.500926418666667</v>
+      </c>
+      <c r="Q12">
+        <v>5.200926418666667</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1219632624362555</v>
+      </c>
+      <c r="T12">
+        <v>1.126163250753359</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.18</v>
+      </c>
+      <c r="W12">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>27.12199645301385</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1132736822159021</v>
+      </c>
+      <c r="C13">
+        <v>32.02498971974915</v>
+      </c>
+      <c r="D13">
+        <v>31.11818971974915</v>
+      </c>
+      <c r="E13">
+        <v>-15.4268</v>
+      </c>
+      <c r="F13">
+        <v>2.8732</v>
+      </c>
+      <c r="G13">
+        <v>3.78</v>
+      </c>
+      <c r="H13">
+        <v>7.82</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K13">
+        <v>2.7</v>
+      </c>
+      <c r="L13">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M13">
+        <v>0.12843204</v>
+      </c>
+      <c r="N13">
+        <v>3.038234626666667</v>
+      </c>
+      <c r="O13">
+        <v>0.5468822328</v>
+      </c>
+      <c r="P13">
+        <v>2.491352393866667</v>
+      </c>
+      <c r="Q13">
+        <v>5.191352393866667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1227435305796653</v>
+      </c>
+      <c r="T13">
+        <v>1.136729326242704</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.18</v>
+      </c>
+      <c r="W13">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>24.65636041183078</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1131150282391743</v>
+      </c>
+      <c r="C14">
+        <v>31.83022345010743</v>
+      </c>
+      <c r="D14">
+        <v>31.18462345010743</v>
+      </c>
+      <c r="E14">
+        <v>-15.1656</v>
+      </c>
+      <c r="F14">
+        <v>3.1344</v>
+      </c>
+      <c r="G14">
+        <v>3.78</v>
+      </c>
+      <c r="H14">
+        <v>7.82</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K14">
+        <v>2.7</v>
+      </c>
+      <c r="L14">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M14">
+        <v>0.14010768</v>
+      </c>
+      <c r="N14">
+        <v>3.026558986666667</v>
+      </c>
+      <c r="O14">
+        <v>0.5447806176000001</v>
+      </c>
+      <c r="P14">
+        <v>2.481778369066667</v>
+      </c>
+      <c r="Q14">
+        <v>5.181778369066667</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1235415320899708</v>
+      </c>
+      <c r="T14">
+        <v>1.147535539811352</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.18</v>
+      </c>
+      <c r="W14">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>22.60166371084488</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1129563742624464</v>
+      </c>
+      <c r="C15">
+        <v>31.6357414439728</v>
+      </c>
+      <c r="D15">
+        <v>31.25134144397281</v>
+      </c>
+      <c r="E15">
+        <v>-14.9044</v>
+      </c>
+      <c r="F15">
+        <v>3.3956</v>
+      </c>
+      <c r="G15">
+        <v>3.78</v>
+      </c>
+      <c r="H15">
+        <v>7.82</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K15">
+        <v>2.7</v>
+      </c>
+      <c r="L15">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M15">
+        <v>0.15178332</v>
+      </c>
+      <c r="N15">
+        <v>3.014883346666667</v>
+      </c>
+      <c r="O15">
+        <v>0.5426790024000001</v>
+      </c>
+      <c r="P15">
+        <v>2.472204344266667</v>
+      </c>
+      <c r="Q15">
+        <v>5.172204344266667</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1243578784625821</v>
+      </c>
+      <c r="T15">
+        <v>1.158590172082728</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.18</v>
+      </c>
+      <c r="W15">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>20.86307419462604</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1127977202857186</v>
+      </c>
+      <c r="C16">
+        <v>31.44154552976113</v>
+      </c>
+      <c r="D16">
+        <v>31.31834552976114</v>
+      </c>
+      <c r="E16">
+        <v>-14.6432</v>
+      </c>
+      <c r="F16">
+        <v>3.6568</v>
+      </c>
+      <c r="G16">
+        <v>3.78</v>
+      </c>
+      <c r="H16">
+        <v>7.82</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K16">
+        <v>2.7</v>
+      </c>
+      <c r="L16">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M16">
+        <v>0.16345896</v>
+      </c>
+      <c r="N16">
+        <v>3.003207706666667</v>
+      </c>
+      <c r="O16">
+        <v>0.5405773872</v>
+      </c>
+      <c r="P16">
+        <v>2.462630319466667</v>
+      </c>
+      <c r="Q16">
+        <v>5.162630319466667</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1251932096345565</v>
+      </c>
+      <c r="T16">
+        <v>1.169901888825531</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.18</v>
+      </c>
+      <c r="W16">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>19.37285460929561</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1126390663089908</v>
+      </c>
+      <c r="C17">
+        <v>31.2476375516028</v>
+      </c>
+      <c r="D17">
+        <v>31.3856375516028</v>
+      </c>
+      <c r="E17">
+        <v>-14.382</v>
+      </c>
+      <c r="F17">
+        <v>3.918</v>
+      </c>
+      <c r="G17">
+        <v>3.78</v>
+      </c>
+      <c r="H17">
+        <v>7.82</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K17">
+        <v>2.7</v>
+      </c>
+      <c r="L17">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M17">
+        <v>0.1751346</v>
+      </c>
+      <c r="N17">
+        <v>2.991532066666667</v>
+      </c>
+      <c r="O17">
+        <v>0.5384757720000001</v>
+      </c>
+      <c r="P17">
+        <v>2.453056294666667</v>
+      </c>
+      <c r="Q17">
+        <v>5.153056294666667</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1260481956576362</v>
+      </c>
+      <c r="T17">
+        <v>1.181479763609341</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.18</v>
+      </c>
+      <c r="W17">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>18.0813309686759</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1124804123322629</v>
+      </c>
+      <c r="C18">
+        <v>31.05401936951183</v>
+      </c>
+      <c r="D18">
+        <v>31.45321936951183</v>
+      </c>
+      <c r="E18">
+        <v>-14.1208</v>
+      </c>
+      <c r="F18">
+        <v>4.1792</v>
+      </c>
+      <c r="G18">
+        <v>3.78</v>
+      </c>
+      <c r="H18">
+        <v>7.82</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K18">
+        <v>2.7</v>
+      </c>
+      <c r="L18">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M18">
+        <v>0.18681024</v>
+      </c>
+      <c r="N18">
+        <v>2.979856426666667</v>
+      </c>
+      <c r="O18">
+        <v>0.5363741568000001</v>
+      </c>
+      <c r="P18">
+        <v>2.443482269866667</v>
+      </c>
+      <c r="Q18">
+        <v>5.143482269866667</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1269235384907892</v>
+      </c>
+      <c r="T18">
+        <v>1.19333330207848</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.18</v>
+      </c>
+      <c r="W18">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>16.95124778313366</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1123217583555351</v>
+      </c>
+      <c r="C19">
+        <v>30.86069285955724</v>
+      </c>
+      <c r="D19">
+        <v>31.52109285955724</v>
+      </c>
+      <c r="E19">
+        <v>-13.8596</v>
+      </c>
+      <c r="F19">
+        <v>4.4404</v>
+      </c>
+      <c r="G19">
+        <v>3.78</v>
+      </c>
+      <c r="H19">
+        <v>7.82</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K19">
+        <v>2.7</v>
+      </c>
+      <c r="L19">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M19">
+        <v>0.19848588</v>
+      </c>
+      <c r="N19">
+        <v>2.968180786666667</v>
+      </c>
+      <c r="O19">
+        <v>0.5342725416</v>
+      </c>
+      <c r="P19">
+        <v>2.433908245066667</v>
+      </c>
+      <c r="Q19">
+        <v>5.133908245066667</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1278199739223314</v>
+      </c>
+      <c r="T19">
+        <v>1.20547246798061</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.18</v>
+      </c>
+      <c r="W19">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>15.95411556059638</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1121631043788073</v>
+      </c>
+      <c r="C20">
+        <v>30.66765991403675</v>
+      </c>
+      <c r="D20">
+        <v>31.58925991403675</v>
+      </c>
+      <c r="E20">
+        <v>-13.5984</v>
+      </c>
+      <c r="F20">
+        <v>4.7016</v>
+      </c>
+      <c r="G20">
+        <v>3.78</v>
+      </c>
+      <c r="H20">
+        <v>7.82</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K20">
+        <v>2.7</v>
+      </c>
+      <c r="L20">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M20">
+        <v>0.21016152</v>
+      </c>
+      <c r="N20">
+        <v>2.956505146666667</v>
+      </c>
+      <c r="O20">
+        <v>0.5321709264</v>
+      </c>
+      <c r="P20">
+        <v>2.424334220266667</v>
+      </c>
+      <c r="Q20">
+        <v>5.124334220266666</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1287382736326918</v>
+      </c>
+      <c r="T20">
+        <v>1.217907711099865</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.18</v>
+      </c>
+      <c r="W20">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>15.06777580722992</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1120044504020794</v>
+      </c>
+      <c r="C21">
+        <v>30.47492244165253</v>
+      </c>
+      <c r="D21">
+        <v>31.65772244165253</v>
+      </c>
+      <c r="E21">
+        <v>-13.3372</v>
+      </c>
+      <c r="F21">
+        <v>4.962800000000001</v>
+      </c>
+      <c r="G21">
+        <v>3.78</v>
+      </c>
+      <c r="H21">
+        <v>7.82</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K21">
+        <v>2.7</v>
+      </c>
+      <c r="L21">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M21">
+        <v>0.22183716</v>
+      </c>
+      <c r="N21">
+        <v>2.944829506666667</v>
+      </c>
+      <c r="O21">
+        <v>0.5300693112</v>
+      </c>
+      <c r="P21">
+        <v>2.414760195466667</v>
+      </c>
+      <c r="Q21">
+        <v>5.114760195466667</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1296792474099746</v>
+      </c>
+      <c r="T21">
+        <v>1.230649997259102</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.18</v>
+      </c>
+      <c r="W21">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>14.27473497527045</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1118457964253516</v>
+      </c>
+      <c r="C22">
+        <v>30.28248236768944</v>
+      </c>
+      <c r="D22">
+        <v>31.72648236768944</v>
+      </c>
+      <c r="E22">
+        <v>-13.076</v>
+      </c>
+      <c r="F22">
+        <v>5.224</v>
+      </c>
+      <c r="G22">
+        <v>3.78</v>
+      </c>
+      <c r="H22">
+        <v>7.82</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K22">
+        <v>2.7</v>
+      </c>
+      <c r="L22">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M22">
+        <v>0.2335128</v>
+      </c>
+      <c r="N22">
+        <v>2.933153866666667</v>
+      </c>
+      <c r="O22">
+        <v>0.527967696</v>
+      </c>
+      <c r="P22">
+        <v>2.405186170666667</v>
+      </c>
+      <c r="Q22">
+        <v>5.105186170666666</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1306437455316895</v>
+      </c>
+      <c r="T22">
+        <v>1.24371084057232</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.18</v>
+      </c>
+      <c r="W22">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>13.56099822650693</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1116871424486238</v>
+      </c>
+      <c r="C23">
+        <v>30.09034163419544</v>
+      </c>
+      <c r="D23">
+        <v>31.79554163419544</v>
+      </c>
+      <c r="E23">
+        <v>-12.8148</v>
+      </c>
+      <c r="F23">
+        <v>5.4852</v>
+      </c>
+      <c r="G23">
+        <v>3.78</v>
+      </c>
+      <c r="H23">
+        <v>7.82</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K23">
+        <v>2.7</v>
+      </c>
+      <c r="L23">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M23">
+        <v>0.24518844</v>
+      </c>
+      <c r="N23">
+        <v>2.921478226666667</v>
+      </c>
+      <c r="O23">
+        <v>0.5258660808</v>
+      </c>
+      <c r="P23">
+        <v>2.395612145866667</v>
+      </c>
+      <c r="Q23">
+        <v>5.095612145866667</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1316326613273718</v>
+      </c>
+      <c r="T23">
+        <v>1.257102338146632</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.18</v>
+      </c>
+      <c r="W23">
+        <v>0.03665400000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>12.91523640619707</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1117269284718959</v>
+      </c>
+      <c r="C24">
+        <v>29.81179525493723</v>
+      </c>
+      <c r="D24">
+        <v>31.77819525493723</v>
+      </c>
+      <c r="E24">
+        <v>-12.5536</v>
+      </c>
+      <c r="F24">
+        <v>5.7464</v>
+      </c>
+      <c r="G24">
+        <v>3.78</v>
+      </c>
+      <c r="H24">
+        <v>7.82</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K24">
+        <v>2.7</v>
+      </c>
+      <c r="L24">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M24">
+        <v>0.26318512</v>
+      </c>
+      <c r="N24">
+        <v>2.903481546666667</v>
+      </c>
+      <c r="O24">
+        <v>0.5226266784</v>
+      </c>
+      <c r="P24">
+        <v>2.380854868266667</v>
+      </c>
+      <c r="Q24">
+        <v>5.080854868266667</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1326469339383281</v>
+      </c>
+      <c r="T24">
+        <v>1.270837207453619</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.18</v>
+      </c>
+      <c r="W24">
+        <v>0.03755600000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>12.03208854158118</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1115772944951681</v>
+      </c>
+      <c r="C25">
+        <v>29.6159329095205</v>
+      </c>
+      <c r="D25">
+        <v>31.8435329095205</v>
+      </c>
+      <c r="E25">
+        <v>-12.2924</v>
+      </c>
+      <c r="F25">
+        <v>6.0076</v>
+      </c>
+      <c r="G25">
+        <v>3.78</v>
+      </c>
+      <c r="H25">
+        <v>7.82</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K25">
+        <v>2.7</v>
+      </c>
+      <c r="L25">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M25">
+        <v>0.27514808</v>
+      </c>
+      <c r="N25">
+        <v>2.891518586666667</v>
+      </c>
+      <c r="O25">
+        <v>0.5204733456</v>
+      </c>
+      <c r="P25">
+        <v>2.371045241066667</v>
+      </c>
+      <c r="Q25">
+        <v>5.071045241066667</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1336875512924261</v>
+      </c>
+      <c r="T25">
+        <v>1.284928826612735</v>
+      </c>
+      <c r="U25">
+        <v>0.0458</v>
+      </c>
+      <c r="V25">
+        <v>0.18</v>
+      </c>
+      <c r="W25">
+        <v>0.03755600000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>11.5089542571646</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1114276605184402</v>
+      </c>
+      <c r="C26">
+        <v>29.4203397930178</v>
+      </c>
+      <c r="D26">
+        <v>31.9091397930178</v>
+      </c>
+      <c r="E26">
+        <v>-12.0312</v>
+      </c>
+      <c r="F26">
+        <v>6.2688</v>
+      </c>
+      <c r="G26">
+        <v>3.78</v>
+      </c>
+      <c r="H26">
+        <v>7.82</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K26">
+        <v>2.7</v>
+      </c>
+      <c r="L26">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M26">
+        <v>0.28711104</v>
+      </c>
+      <c r="N26">
+        <v>2.879555626666667</v>
+      </c>
+      <c r="O26">
+        <v>0.5183200128000001</v>
+      </c>
+      <c r="P26">
+        <v>2.361235613866667</v>
+      </c>
+      <c r="Q26">
+        <v>5.061235613866667</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1347555533137372</v>
+      </c>
+      <c r="T26">
+        <v>1.299391277854986</v>
+      </c>
+      <c r="U26">
+        <v>0.0458</v>
+      </c>
+      <c r="V26">
+        <v>0.18</v>
+      </c>
+      <c r="W26">
+        <v>0.03755600000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.02941449644941</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1112780265417124</v>
+      </c>
+      <c r="C27">
+        <v>29.22501757293287</v>
+      </c>
+      <c r="D27">
+        <v>31.97501757293287</v>
+      </c>
+      <c r="E27">
+        <v>-11.77</v>
+      </c>
+      <c r="F27">
+        <v>6.53</v>
+      </c>
+      <c r="G27">
+        <v>3.78</v>
+      </c>
+      <c r="H27">
+        <v>7.82</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K27">
+        <v>2.7</v>
+      </c>
+      <c r="L27">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M27">
+        <v>0.299074</v>
+      </c>
+      <c r="N27">
+        <v>2.867592666666667</v>
+      </c>
+      <c r="O27">
+        <v>0.51616668</v>
+      </c>
+      <c r="P27">
+        <v>2.351425986666667</v>
+      </c>
+      <c r="Q27">
+        <v>5.051425986666667</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1358520353889499</v>
+      </c>
+      <c r="T27">
+        <v>1.314239394463697</v>
+      </c>
+      <c r="U27">
+        <v>0.0458</v>
+      </c>
+      <c r="V27">
+        <v>0.18</v>
+      </c>
+      <c r="W27">
+        <v>0.03755600000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>10.58823791659144</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1111283925649846</v>
+      </c>
+      <c r="C28">
+        <v>29.02996793056845</v>
+      </c>
+      <c r="D28">
+        <v>32.04116793056845</v>
+      </c>
+      <c r="E28">
+        <v>-11.5088</v>
+      </c>
+      <c r="F28">
+        <v>6.791200000000001</v>
+      </c>
+      <c r="G28">
+        <v>3.78</v>
+      </c>
+      <c r="H28">
+        <v>7.82</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K28">
+        <v>2.7</v>
+      </c>
+      <c r="L28">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M28">
+        <v>0.31103696</v>
+      </c>
+      <c r="N28">
+        <v>2.855629706666667</v>
+      </c>
+      <c r="O28">
+        <v>0.5140133472</v>
+      </c>
+      <c r="P28">
+        <v>2.341616359466667</v>
+      </c>
+      <c r="Q28">
+        <v>5.041616359466667</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.136978152114844</v>
+      </c>
+      <c r="T28">
+        <v>1.329488811521291</v>
+      </c>
+      <c r="U28">
+        <v>0.0458</v>
+      </c>
+      <c r="V28">
+        <v>0.18</v>
+      </c>
+      <c r="W28">
+        <v>0.03755600000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>10.18099799672253</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1114658385882567</v>
+      </c>
+      <c r="C29">
+        <v>28.61997497765931</v>
+      </c>
+      <c r="D29">
+        <v>31.89237497765931</v>
+      </c>
+      <c r="E29">
+        <v>-11.2476</v>
+      </c>
+      <c r="F29">
+        <v>7.0524</v>
+      </c>
+      <c r="G29">
+        <v>3.78</v>
+      </c>
+      <c r="H29">
+        <v>7.82</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K29">
+        <v>2.7</v>
+      </c>
+      <c r="L29">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M29">
+        <v>0.3385152</v>
+      </c>
+      <c r="N29">
+        <v>2.828151466666667</v>
+      </c>
+      <c r="O29">
+        <v>0.509067264</v>
+      </c>
+      <c r="P29">
+        <v>2.319084202666667</v>
+      </c>
+      <c r="Q29">
+        <v>5.019084202666667</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1381351213537764</v>
+      </c>
+      <c r="T29">
+        <v>1.345156020827039</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.18</v>
+      </c>
+      <c r="W29">
+        <v>0.03936000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>9.354577480321909</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1113342446115289</v>
+      </c>
+      <c r="C30">
+        <v>28.41663515767611</v>
+      </c>
+      <c r="D30">
+        <v>31.95023515767611</v>
+      </c>
+      <c r="E30">
+        <v>-10.9864</v>
+      </c>
+      <c r="F30">
+        <v>7.313600000000001</v>
+      </c>
+      <c r="G30">
+        <v>3.78</v>
+      </c>
+      <c r="H30">
+        <v>7.82</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K30">
+        <v>2.7</v>
+      </c>
+      <c r="L30">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M30">
+        <v>0.3510528000000001</v>
+      </c>
+      <c r="N30">
+        <v>2.815613866666667</v>
+      </c>
+      <c r="O30">
+        <v>0.5068104960000001</v>
+      </c>
+      <c r="P30">
+        <v>2.308803370666667</v>
+      </c>
+      <c r="Q30">
+        <v>5.008803370666667</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1393242286271235</v>
+      </c>
+      <c r="T30">
+        <v>1.361258430391281</v>
+      </c>
+      <c r="U30">
+        <v>0.048</v>
+      </c>
+      <c r="V30">
+        <v>0.18</v>
+      </c>
+      <c r="W30">
+        <v>0.03936000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>9.020485427453268</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1112026506348011</v>
+      </c>
+      <c r="C31">
+        <v>28.2135056628983</v>
+      </c>
+      <c r="D31">
+        <v>32.0083056628983</v>
+      </c>
+      <c r="E31">
+        <v>-10.7252</v>
+      </c>
+      <c r="F31">
+        <v>7.5748</v>
+      </c>
+      <c r="G31">
+        <v>3.78</v>
+      </c>
+      <c r="H31">
+        <v>7.82</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K31">
+        <v>2.7</v>
+      </c>
+      <c r="L31">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M31">
+        <v>0.3635904</v>
+      </c>
+      <c r="N31">
+        <v>2.803076266666667</v>
+      </c>
+      <c r="O31">
+        <v>0.504553728</v>
+      </c>
+      <c r="P31">
+        <v>2.298522538666667</v>
+      </c>
+      <c r="Q31">
+        <v>4.998522538666667</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1405468318800015</v>
+      </c>
+      <c r="T31">
+        <v>1.377814428957331</v>
+      </c>
+      <c r="U31">
+        <v>0.048</v>
+      </c>
+      <c r="V31">
+        <v>0.18</v>
+      </c>
+      <c r="W31">
+        <v>0.03936000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>8.709434205816949</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1110710566580732</v>
+      </c>
+      <c r="C32">
+        <v>28.01058764223104</v>
+      </c>
+      <c r="D32">
+        <v>32.06658764223104</v>
+      </c>
+      <c r="E32">
+        <v>-10.464</v>
+      </c>
+      <c r="F32">
+        <v>7.836</v>
+      </c>
+      <c r="G32">
+        <v>3.78</v>
+      </c>
+      <c r="H32">
+        <v>7.82</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K32">
+        <v>2.7</v>
+      </c>
+      <c r="L32">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M32">
+        <v>0.376128</v>
+      </c>
+      <c r="N32">
+        <v>2.790538666666667</v>
+      </c>
+      <c r="O32">
+        <v>0.50229696</v>
+      </c>
+      <c r="P32">
+        <v>2.288241706666667</v>
+      </c>
+      <c r="Q32">
+        <v>4.988241706666667</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1418043666543903</v>
+      </c>
+      <c r="T32">
+        <v>1.394843456053841</v>
+      </c>
+      <c r="U32">
+        <v>0.048</v>
+      </c>
+      <c r="V32">
+        <v>0.18</v>
+      </c>
+      <c r="W32">
+        <v>0.03936000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.419119732289717</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1109394626813454</v>
+      </c>
+      <c r="C33">
+        <v>27.80788225296264</v>
+      </c>
+      <c r="D33">
+        <v>32.12508225296264</v>
+      </c>
+      <c r="E33">
+        <v>-10.2028</v>
+      </c>
+      <c r="F33">
+        <v>8.097200000000001</v>
+      </c>
+      <c r="G33">
+        <v>3.78</v>
+      </c>
+      <c r="H33">
+        <v>7.82</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K33">
+        <v>2.7</v>
+      </c>
+      <c r="L33">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M33">
+        <v>0.3886656000000001</v>
+      </c>
+      <c r="N33">
+        <v>2.778001066666667</v>
+      </c>
+      <c r="O33">
+        <v>0.500040192</v>
+      </c>
+      <c r="P33">
+        <v>2.277960874666667</v>
+      </c>
+      <c r="Q33">
+        <v>4.977960874666667</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1430983517120948</v>
+      </c>
+      <c r="T33">
+        <v>1.412366078138655</v>
+      </c>
+      <c r="U33">
+        <v>0.048</v>
+      </c>
+      <c r="V33">
+        <v>0.18</v>
+      </c>
+      <c r="W33">
+        <v>0.03936000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.147535224796499</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1108078687046176</v>
+      </c>
+      <c r="C34">
+        <v>27.6053906608412</v>
+      </c>
+      <c r="D34">
+        <v>32.1837906608412</v>
+      </c>
+      <c r="E34">
+        <v>-9.941600000000001</v>
+      </c>
+      <c r="F34">
+        <v>8.3584</v>
+      </c>
+      <c r="G34">
+        <v>3.78</v>
+      </c>
+      <c r="H34">
+        <v>7.82</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K34">
+        <v>2.7</v>
+      </c>
+      <c r="L34">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M34">
+        <v>0.4012032</v>
+      </c>
+      <c r="N34">
+        <v>2.765463466666667</v>
+      </c>
+      <c r="O34">
+        <v>0.4977834240000001</v>
+      </c>
+      <c r="P34">
+        <v>2.267680042666667</v>
+      </c>
+      <c r="Q34">
+        <v>4.967680042666667</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1444303951538494</v>
+      </c>
+      <c r="T34">
+        <v>1.430404071461258</v>
+      </c>
+      <c r="U34">
+        <v>0.048</v>
+      </c>
+      <c r="V34">
+        <v>0.18</v>
+      </c>
+      <c r="W34">
+        <v>0.03936000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>7.892924749021611</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1110821747278897</v>
+      </c>
+      <c r="C35">
+        <v>27.22205532577092</v>
+      </c>
+      <c r="D35">
+        <v>32.06165532577092</v>
+      </c>
+      <c r="E35">
+        <v>-9.680400000000001</v>
+      </c>
+      <c r="F35">
+        <v>8.6196</v>
+      </c>
+      <c r="G35">
+        <v>3.78</v>
+      </c>
+      <c r="H35">
+        <v>7.82</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K35">
+        <v>2.7</v>
+      </c>
+      <c r="L35">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M35">
+        <v>0.4266702000000001</v>
+      </c>
+      <c r="N35">
+        <v>2.739996466666667</v>
+      </c>
+      <c r="O35">
+        <v>0.493199364</v>
+      </c>
+      <c r="P35">
+        <v>2.246797102666667</v>
+      </c>
+      <c r="Q35">
+        <v>4.946797102666666</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1458022010864026</v>
+      </c>
+      <c r="T35">
+        <v>1.448980512345729</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.18</v>
+      </c>
+      <c r="W35">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.421813538106637</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1109628807511619</v>
+      </c>
+      <c r="C36">
+        <v>27.01385712287873</v>
+      </c>
+      <c r="D36">
+        <v>32.11465712287873</v>
+      </c>
+      <c r="E36">
+        <v>-9.4192</v>
+      </c>
+      <c r="F36">
+        <v>8.880800000000001</v>
+      </c>
+      <c r="G36">
+        <v>3.78</v>
+      </c>
+      <c r="H36">
+        <v>7.82</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K36">
+        <v>2.7</v>
+      </c>
+      <c r="L36">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M36">
+        <v>0.4395996</v>
+      </c>
+      <c r="N36">
+        <v>2.727067066666667</v>
+      </c>
+      <c r="O36">
+        <v>0.490872072</v>
+      </c>
+      <c r="P36">
+        <v>2.236194994666667</v>
+      </c>
+      <c r="Q36">
+        <v>4.936194994666667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1472155768956999</v>
+      </c>
+      <c r="T36">
+        <v>1.468119875681245</v>
+      </c>
+      <c r="U36">
+        <v>0.0495</v>
+      </c>
+      <c r="V36">
+        <v>0.18</v>
+      </c>
+      <c r="W36">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.203524904632912</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1108435867744341</v>
+      </c>
+      <c r="C37">
+        <v>26.80583444692611</v>
+      </c>
+      <c r="D37">
+        <v>32.16783444692611</v>
+      </c>
+      <c r="E37">
+        <v>-9.157999999999999</v>
+      </c>
+      <c r="F37">
+        <v>9.142000000000001</v>
+      </c>
+      <c r="G37">
+        <v>3.78</v>
+      </c>
+      <c r="H37">
+        <v>7.82</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K37">
+        <v>2.7</v>
+      </c>
+      <c r="L37">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M37">
+        <v>0.4525290000000001</v>
+      </c>
+      <c r="N37">
+        <v>2.714137666666667</v>
+      </c>
+      <c r="O37">
+        <v>0.48854478</v>
+      </c>
+      <c r="P37">
+        <v>2.225592886666667</v>
+      </c>
+      <c r="Q37">
+        <v>4.925592886666667</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.148672441191437</v>
+      </c>
+      <c r="T37">
+        <v>1.487848142504008</v>
+      </c>
+      <c r="U37">
+        <v>0.0495</v>
+      </c>
+      <c r="V37">
+        <v>0.18</v>
+      </c>
+      <c r="W37">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>6.997709907357686</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1107242927977062</v>
+      </c>
+      <c r="C38">
+        <v>26.59798817130251</v>
+      </c>
+      <c r="D38">
+        <v>32.22118817130251</v>
+      </c>
+      <c r="E38">
+        <v>-8.896800000000001</v>
+      </c>
+      <c r="F38">
+        <v>9.4032</v>
+      </c>
+      <c r="G38">
+        <v>3.78</v>
+      </c>
+      <c r="H38">
+        <v>7.82</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K38">
+        <v>2.7</v>
+      </c>
+      <c r="L38">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M38">
+        <v>0.4654584</v>
+      </c>
+      <c r="N38">
+        <v>2.701208266666667</v>
+      </c>
+      <c r="O38">
+        <v>0.486217488</v>
+      </c>
+      <c r="P38">
+        <v>2.214990778666667</v>
+      </c>
+      <c r="Q38">
+        <v>4.914990778666667</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.150174832496416</v>
+      </c>
+      <c r="T38">
+        <v>1.508192917664982</v>
+      </c>
+      <c r="U38">
+        <v>0.0495</v>
+      </c>
+      <c r="V38">
+        <v>0.18</v>
+      </c>
+      <c r="W38">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.803329076597752</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1106049988209784</v>
+      </c>
+      <c r="C39">
+        <v>26.39031917520146</v>
+      </c>
+      <c r="D39">
+        <v>32.27471917520146</v>
+      </c>
+      <c r="E39">
+        <v>-8.6356</v>
+      </c>
+      <c r="F39">
+        <v>9.664400000000001</v>
+      </c>
+      <c r="G39">
+        <v>3.78</v>
+      </c>
+      <c r="H39">
+        <v>7.82</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K39">
+        <v>2.7</v>
+      </c>
+      <c r="L39">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M39">
+        <v>0.4783878</v>
+      </c>
+      <c r="N39">
+        <v>2.688278866666667</v>
+      </c>
+      <c r="O39">
+        <v>0.483890196</v>
+      </c>
+      <c r="P39">
+        <v>2.204388670666667</v>
+      </c>
+      <c r="Q39">
+        <v>4.904388670666667</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1517249187634578</v>
+      </c>
+      <c r="T39">
+        <v>1.529183558704082</v>
+      </c>
+      <c r="U39">
+        <v>0.0495</v>
+      </c>
+      <c r="V39">
+        <v>0.18</v>
+      </c>
+      <c r="W39">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.619455317770785</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1104857048442506</v>
+      </c>
+      <c r="C40">
+        <v>26.18282834366886</v>
+      </c>
+      <c r="D40">
+        <v>32.32842834366886</v>
+      </c>
+      <c r="E40">
+        <v>-8.3744</v>
+      </c>
+      <c r="F40">
+        <v>9.925600000000001</v>
+      </c>
+      <c r="G40">
+        <v>3.78</v>
+      </c>
+      <c r="H40">
+        <v>7.82</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K40">
+        <v>2.7</v>
+      </c>
+      <c r="L40">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M40">
+        <v>0.4913172000000001</v>
+      </c>
+      <c r="N40">
+        <v>2.675349466666667</v>
+      </c>
+      <c r="O40">
+        <v>0.481562904</v>
+      </c>
+      <c r="P40">
+        <v>2.193786562666667</v>
+      </c>
+      <c r="Q40">
+        <v>4.893786562666667</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1533250078133074</v>
+      </c>
+      <c r="T40">
+        <v>1.550851317196056</v>
+      </c>
+      <c r="U40">
+        <v>0.0495</v>
+      </c>
+      <c r="V40">
+        <v>0.18</v>
+      </c>
+      <c r="W40">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.445259125197869</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1103664108675227</v>
+      </c>
+      <c r="C41">
+        <v>25.9755165676517</v>
+      </c>
+      <c r="D41">
+        <v>32.3823165676517</v>
+      </c>
+      <c r="E41">
+        <v>-8.113200000000001</v>
+      </c>
+      <c r="F41">
+        <v>10.1868</v>
+      </c>
+      <c r="G41">
+        <v>3.78</v>
+      </c>
+      <c r="H41">
+        <v>7.82</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K41">
+        <v>2.7</v>
+      </c>
+      <c r="L41">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M41">
+        <v>0.5042466</v>
+      </c>
+      <c r="N41">
+        <v>2.662420066666667</v>
+      </c>
+      <c r="O41">
+        <v>0.479235612</v>
+      </c>
+      <c r="P41">
+        <v>2.183184454666667</v>
+      </c>
+      <c r="Q41">
+        <v>4.883184454666667</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1549775587992176</v>
+      </c>
+      <c r="T41">
+        <v>1.573229493999243</v>
+      </c>
+      <c r="U41">
+        <v>0.0495</v>
+      </c>
+      <c r="V41">
+        <v>0.18</v>
+      </c>
+      <c r="W41">
+        <v>0.04059000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.279996070705617</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1107063168907949</v>
+      </c>
+      <c r="C42">
+        <v>25.56124316708291</v>
+      </c>
+      <c r="D42">
+        <v>32.22924316708291</v>
+      </c>
+      <c r="E42">
+        <v>-7.852</v>
+      </c>
+      <c r="F42">
+        <v>10.448</v>
+      </c>
+      <c r="G42">
+        <v>3.78</v>
+      </c>
+      <c r="H42">
+        <v>7.82</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K42">
+        <v>2.7</v>
+      </c>
+      <c r="L42">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M42">
+        <v>0.5318032</v>
+      </c>
+      <c r="N42">
+        <v>2.634863466666667</v>
+      </c>
+      <c r="O42">
+        <v>0.474275424</v>
+      </c>
+      <c r="P42">
+        <v>2.160588042666667</v>
+      </c>
+      <c r="Q42">
+        <v>4.860588042666667</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1566851948179915</v>
+      </c>
+      <c r="T42">
+        <v>1.596353610029202</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.18</v>
+      </c>
+      <c r="W42">
+        <v>0.041738</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.954583700637128</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.110598502914067</v>
+      </c>
+      <c r="C43">
+        <v>25.34843920226113</v>
+      </c>
+      <c r="D43">
+        <v>32.27763920226113</v>
+      </c>
+      <c r="E43">
+        <v>-7.5908</v>
+      </c>
+      <c r="F43">
+        <v>10.7092</v>
+      </c>
+      <c r="G43">
+        <v>3.78</v>
+      </c>
+      <c r="H43">
+        <v>7.82</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K43">
+        <v>2.7</v>
+      </c>
+      <c r="L43">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M43">
+        <v>0.54509828</v>
+      </c>
+      <c r="N43">
+        <v>2.621568386666667</v>
+      </c>
+      <c r="O43">
+        <v>0.4718823096</v>
+      </c>
+      <c r="P43">
+        <v>2.149686077066667</v>
+      </c>
+      <c r="Q43">
+        <v>4.849686077066667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1584507168035035</v>
+      </c>
+      <c r="T43">
+        <v>1.62026159439916</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.18</v>
+      </c>
+      <c r="W43">
+        <v>0.041738</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.8093499518411</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1104906889373392</v>
+      </c>
+      <c r="C44">
+        <v>25.13578080080572</v>
+      </c>
+      <c r="D44">
+        <v>32.32618080080572</v>
+      </c>
+      <c r="E44">
+        <v>-7.329600000000001</v>
+      </c>
+      <c r="F44">
+        <v>10.9704</v>
+      </c>
+      <c r="G44">
+        <v>3.78</v>
+      </c>
+      <c r="H44">
+        <v>7.82</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K44">
+        <v>2.7</v>
+      </c>
+      <c r="L44">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M44">
+        <v>0.5583933599999999</v>
+      </c>
+      <c r="N44">
+        <v>2.608273306666667</v>
+      </c>
+      <c r="O44">
+        <v>0.4694891952</v>
+      </c>
+      <c r="P44">
+        <v>2.138784111466667</v>
+      </c>
+      <c r="Q44">
+        <v>4.838784111466667</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1602771188574814</v>
+      </c>
+      <c r="T44">
+        <v>1.644993992023255</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.18</v>
+      </c>
+      <c r="W44">
+        <v>0.041738</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.671032095844884</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1103828749606114</v>
+      </c>
+      <c r="C45">
+        <v>24.92326862043402</v>
+      </c>
+      <c r="D45">
+        <v>32.37486862043402</v>
+      </c>
+      <c r="E45">
+        <v>-7.0684</v>
+      </c>
+      <c r="F45">
+        <v>11.2316</v>
+      </c>
+      <c r="G45">
+        <v>3.78</v>
+      </c>
+      <c r="H45">
+        <v>7.82</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K45">
+        <v>2.7</v>
+      </c>
+      <c r="L45">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M45">
+        <v>0.5716884400000001</v>
+      </c>
+      <c r="N45">
+        <v>2.594978226666667</v>
+      </c>
+      <c r="O45">
+        <v>0.4670960808</v>
+      </c>
+      <c r="P45">
+        <v>2.127882145866667</v>
+      </c>
+      <c r="Q45">
+        <v>4.827882145866667</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.162167605194055</v>
+      </c>
+      <c r="T45">
+        <v>1.670594193072756</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.18</v>
+      </c>
+      <c r="W45">
+        <v>0.041738</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.539147628499654</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1102750609838836</v>
+      </c>
+      <c r="C46">
+        <v>24.71090332283178</v>
+      </c>
+      <c r="D46">
+        <v>32.42370332283178</v>
+      </c>
+      <c r="E46">
+        <v>-6.8072</v>
+      </c>
+      <c r="F46">
+        <v>11.4928</v>
+      </c>
+      <c r="G46">
+        <v>3.78</v>
+      </c>
+      <c r="H46">
+        <v>7.82</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K46">
+        <v>2.7</v>
+      </c>
+      <c r="L46">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M46">
+        <v>0.5849835200000001</v>
+      </c>
+      <c r="N46">
+        <v>2.581683146666667</v>
+      </c>
+      <c r="O46">
+        <v>0.4647029664</v>
+      </c>
+      <c r="P46">
+        <v>2.116980180266667</v>
+      </c>
+      <c r="Q46">
+        <v>4.816980180266667</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1641256088997921</v>
+      </c>
+      <c r="T46">
+        <v>1.697108687016883</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.18</v>
+      </c>
+      <c r="W46">
+        <v>0.041738</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.413257909670116</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1101672470071557</v>
+      </c>
+      <c r="C47">
+        <v>24.49868557368319</v>
+      </c>
+      <c r="D47">
+        <v>32.47268557368319</v>
+      </c>
+      <c r="E47">
+        <v>-6.545999999999999</v>
+      </c>
+      <c r="F47">
+        <v>11.754</v>
+      </c>
+      <c r="G47">
+        <v>3.78</v>
+      </c>
+      <c r="H47">
+        <v>7.82</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K47">
+        <v>2.7</v>
+      </c>
+      <c r="L47">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M47">
+        <v>0.5982786000000001</v>
+      </c>
+      <c r="N47">
+        <v>2.568388066666667</v>
+      </c>
+      <c r="O47">
+        <v>0.462309852</v>
+      </c>
+      <c r="P47">
+        <v>2.106078214666667</v>
+      </c>
+      <c r="Q47">
+        <v>4.806078214666667</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1661548127402831</v>
+      </c>
+      <c r="T47">
+        <v>1.724587344377159</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.18</v>
+      </c>
+      <c r="W47">
+        <v>0.041738</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.292963289455225</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1100594330304279</v>
+      </c>
+      <c r="C48">
+        <v>24.28661604270103</v>
+      </c>
+      <c r="D48">
+        <v>32.52181604270103</v>
+      </c>
+      <c r="E48">
+        <v>-6.284800000000001</v>
+      </c>
+      <c r="F48">
+        <v>12.0152</v>
+      </c>
+      <c r="G48">
+        <v>3.78</v>
+      </c>
+      <c r="H48">
+        <v>7.82</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K48">
+        <v>2.7</v>
+      </c>
+      <c r="L48">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M48">
+        <v>0.61157368</v>
+      </c>
+      <c r="N48">
+        <v>2.555092986666667</v>
+      </c>
+      <c r="O48">
+        <v>0.4599167376</v>
+      </c>
+      <c r="P48">
+        <v>2.095176249066667</v>
+      </c>
+      <c r="Q48">
+        <v>4.795176249066667</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1682591722785702</v>
+      </c>
+      <c r="T48">
+        <v>1.753083729787816</v>
+      </c>
+      <c r="U48">
+        <v>0.0509</v>
+      </c>
+      <c r="V48">
+        <v>0.18</v>
+      </c>
+      <c r="W48">
+        <v>0.041738</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.177898870119241</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1099516190537001</v>
+      </c>
+      <c r="C49">
+        <v>24.07469540365737</v>
+      </c>
+      <c r="D49">
+        <v>32.57109540365737</v>
+      </c>
+      <c r="E49">
+        <v>-6.0236</v>
+      </c>
+      <c r="F49">
+        <v>12.2764</v>
+      </c>
+      <c r="G49">
+        <v>3.78</v>
+      </c>
+      <c r="H49">
+        <v>7.82</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K49">
+        <v>2.7</v>
+      </c>
+      <c r="L49">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M49">
+        <v>0.62486876</v>
+      </c>
+      <c r="N49">
+        <v>2.541797906666667</v>
+      </c>
+      <c r="O49">
+        <v>0.4575236232</v>
+      </c>
+      <c r="P49">
+        <v>2.084274283466667</v>
+      </c>
+      <c r="Q49">
+        <v>4.784274283466667</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1704429416107548</v>
+      </c>
+      <c r="T49">
+        <v>1.782655450496989</v>
+      </c>
+      <c r="U49">
+        <v>0.0509</v>
+      </c>
+      <c r="V49">
+        <v>0.18</v>
+      </c>
+      <c r="W49">
+        <v>0.041738</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.067730809052875</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1098438050769722</v>
+      </c>
+      <c r="C50">
+        <v>23.86292433441419</v>
+      </c>
+      <c r="D50">
+        <v>32.62052433441418</v>
+      </c>
+      <c r="E50">
+        <v>-5.762400000000001</v>
+      </c>
+      <c r="F50">
+        <v>12.5376</v>
+      </c>
+      <c r="G50">
+        <v>3.78</v>
+      </c>
+      <c r="H50">
+        <v>7.82</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K50">
+        <v>2.7</v>
+      </c>
+      <c r="L50">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M50">
+        <v>0.6381638399999999</v>
+      </c>
+      <c r="N50">
+        <v>2.528502826666667</v>
+      </c>
+      <c r="O50">
+        <v>0.4551305088000001</v>
+      </c>
+      <c r="P50">
+        <v>2.073372317866667</v>
+      </c>
+      <c r="Q50">
+        <v>4.773372317866667</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1727107020711004</v>
+      </c>
+      <c r="T50">
+        <v>1.813364545079591</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.18</v>
+      </c>
+      <c r="W50">
+        <v>0.041738</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.962153083864274</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1097359911002444</v>
+      </c>
+      <c r="C51">
+        <v>23.65130351695455</v>
+      </c>
+      <c r="D51">
+        <v>32.67010351695455</v>
+      </c>
+      <c r="E51">
+        <v>-5.501200000000001</v>
+      </c>
+      <c r="F51">
+        <v>12.7988</v>
+      </c>
+      <c r="G51">
+        <v>3.78</v>
+      </c>
+      <c r="H51">
+        <v>7.82</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K51">
+        <v>2.7</v>
+      </c>
+      <c r="L51">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M51">
+        <v>0.6514589200000001</v>
+      </c>
+      <c r="N51">
+        <v>2.515207746666667</v>
+      </c>
+      <c r="O51">
+        <v>0.4527373944</v>
+      </c>
+      <c r="P51">
+        <v>2.062470352266667</v>
+      </c>
+      <c r="Q51">
+        <v>4.762470352266667</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1750673943142046</v>
+      </c>
+      <c r="T51">
+        <v>1.845277917881119</v>
+      </c>
+      <c r="U51">
+        <v>0.0509</v>
+      </c>
+      <c r="V51">
+        <v>0.18</v>
+      </c>
+      <c r="W51">
+        <v>0.041738</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.860884653581329</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1096281771235165</v>
+      </c>
+      <c r="C52">
+        <v>23.43983363741395</v>
+      </c>
+      <c r="D52">
+        <v>32.71983363741396</v>
+      </c>
+      <c r="E52">
+        <v>-5.24</v>
+      </c>
+      <c r="F52">
+        <v>13.06</v>
+      </c>
+      <c r="G52">
+        <v>3.78</v>
+      </c>
+      <c r="H52">
+        <v>7.82</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K52">
+        <v>2.7</v>
+      </c>
+      <c r="L52">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M52">
+        <v>0.6647540000000001</v>
+      </c>
+      <c r="N52">
+        <v>2.501912666666667</v>
+      </c>
+      <c r="O52">
+        <v>0.45034428</v>
+      </c>
+      <c r="P52">
+        <v>2.051568386666667</v>
+      </c>
+      <c r="Q52">
+        <v>4.751568386666667</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1775183542470331</v>
+      </c>
+      <c r="T52">
+        <v>1.878467825594707</v>
+      </c>
+      <c r="U52">
+        <v>0.0509</v>
+      </c>
+      <c r="V52">
+        <v>0.18</v>
+      </c>
+      <c r="W52">
+        <v>0.041738</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.763666960509703</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1095203631467887</v>
+      </c>
+      <c r="C53">
+        <v>23.22851538611199</v>
+      </c>
+      <c r="D53">
+        <v>32.76971538611199</v>
+      </c>
+      <c r="E53">
+        <v>-4.9788</v>
+      </c>
+      <c r="F53">
+        <v>13.3212</v>
+      </c>
+      <c r="G53">
+        <v>3.78</v>
+      </c>
+      <c r="H53">
+        <v>7.82</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K53">
+        <v>2.7</v>
+      </c>
+      <c r="L53">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M53">
+        <v>0.6780490800000001</v>
+      </c>
+      <c r="N53">
+        <v>2.488617586666667</v>
+      </c>
+      <c r="O53">
+        <v>0.4479511656</v>
+      </c>
+      <c r="P53">
+        <v>2.040666421066667</v>
+      </c>
+      <c r="Q53">
+        <v>4.740666421066667</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1800693533607933</v>
+      </c>
+      <c r="T53">
+        <v>1.913012423419055</v>
+      </c>
+      <c r="U53">
+        <v>0.0509</v>
+      </c>
+      <c r="V53">
+        <v>0.18</v>
+      </c>
+      <c r="W53">
+        <v>0.041738</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.670261725989905</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1094125491700609</v>
+      </c>
+      <c r="C54">
+        <v>23.01734945758431</v>
+      </c>
+      <c r="D54">
+        <v>32.81974945758431</v>
+      </c>
+      <c r="E54">
+        <v>-4.717599999999999</v>
+      </c>
+      <c r="F54">
+        <v>13.5824</v>
+      </c>
+      <c r="G54">
+        <v>3.78</v>
+      </c>
+      <c r="H54">
+        <v>7.82</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K54">
+        <v>2.7</v>
+      </c>
+      <c r="L54">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M54">
+        <v>0.6913441600000001</v>
+      </c>
+      <c r="N54">
+        <v>2.475322506666667</v>
+      </c>
+      <c r="O54">
+        <v>0.4455580512000001</v>
+      </c>
+      <c r="P54">
+        <v>2.029764455466667</v>
+      </c>
+      <c r="Q54">
+        <v>4.729764455466667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1827266441042935</v>
+      </c>
+      <c r="T54">
+        <v>1.948996379486084</v>
+      </c>
+      <c r="U54">
+        <v>0.0509</v>
+      </c>
+      <c r="V54">
+        <v>0.18</v>
+      </c>
+      <c r="W54">
+        <v>0.041738</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.580449000490098</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.110434695193333</v>
+      </c>
+      <c r="C55">
+        <v>22.28784877866997</v>
+      </c>
+      <c r="D55">
+        <v>32.35144877866997</v>
+      </c>
+      <c r="E55">
+        <v>-4.4564</v>
+      </c>
+      <c r="F55">
+        <v>13.8436</v>
+      </c>
+      <c r="G55">
+        <v>3.78</v>
+      </c>
+      <c r="H55">
+        <v>7.82</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K55">
+        <v>2.7</v>
+      </c>
+      <c r="L55">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M55">
+        <v>0.7406326</v>
+      </c>
+      <c r="N55">
+        <v>2.426034066666667</v>
+      </c>
+      <c r="O55">
+        <v>0.436686132</v>
+      </c>
+      <c r="P55">
+        <v>1.989347934666667</v>
+      </c>
+      <c r="Q55">
+        <v>4.689347934666667</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1854970110496448</v>
+      </c>
+      <c r="T55">
+        <v>1.986511567726178</v>
+      </c>
+      <c r="U55">
+        <v>0.0535</v>
+      </c>
+      <c r="V55">
+        <v>0.18</v>
+      </c>
+      <c r="W55">
+        <v>0.04387</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.275624198376722</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1103482012166052</v>
+      </c>
+      <c r="C56">
+        <v>22.06575815403083</v>
+      </c>
+      <c r="D56">
+        <v>32.39055815403083</v>
+      </c>
+      <c r="E56">
+        <v>-4.1952</v>
+      </c>
+      <c r="F56">
+        <v>14.1048</v>
+      </c>
+      <c r="G56">
+        <v>3.78</v>
+      </c>
+      <c r="H56">
+        <v>7.82</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K56">
+        <v>2.7</v>
+      </c>
+      <c r="L56">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M56">
+        <v>0.7546068</v>
+      </c>
+      <c r="N56">
+        <v>2.412059866666667</v>
+      </c>
+      <c r="O56">
+        <v>0.434170776</v>
+      </c>
+      <c r="P56">
+        <v>1.977889090666667</v>
+      </c>
+      <c r="Q56">
+        <v>4.677889090666667</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1883878287317504</v>
+      </c>
+      <c r="T56">
+        <v>2.025657851107145</v>
+      </c>
+      <c r="U56">
+        <v>0.0535</v>
+      </c>
+      <c r="V56">
+        <v>0.18</v>
+      </c>
+      <c r="W56">
+        <v>0.04387</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.196445972480856</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1102617072398774</v>
+      </c>
+      <c r="C57">
+        <v>21.84376220178429</v>
+      </c>
+      <c r="D57">
+        <v>32.42976220178429</v>
+      </c>
+      <c r="E57">
+        <v>-3.933999999999999</v>
+      </c>
+      <c r="F57">
+        <v>14.366</v>
+      </c>
+      <c r="G57">
+        <v>3.78</v>
+      </c>
+      <c r="H57">
+        <v>7.82</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K57">
+        <v>2.7</v>
+      </c>
+      <c r="L57">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M57">
+        <v>0.7685810000000001</v>
+      </c>
+      <c r="N57">
+        <v>2.398085666666667</v>
+      </c>
+      <c r="O57">
+        <v>0.43165542</v>
+      </c>
+      <c r="P57">
+        <v>1.966430246666667</v>
+      </c>
+      <c r="Q57">
+        <v>4.666430246666667</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1914071271997275</v>
+      </c>
+      <c r="T57">
+        <v>2.066543969305045</v>
+      </c>
+      <c r="U57">
+        <v>0.0535</v>
+      </c>
+      <c r="V57">
+        <v>0.18</v>
+      </c>
+      <c r="W57">
+        <v>0.04387</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.120146954799385</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1101752132631495</v>
+      </c>
+      <c r="C58">
+        <v>21.62186126610833</v>
+      </c>
+      <c r="D58">
+        <v>32.46906126610833</v>
+      </c>
+      <c r="E58">
+        <v>-3.672799999999999</v>
+      </c>
+      <c r="F58">
+        <v>14.6272</v>
+      </c>
+      <c r="G58">
+        <v>3.78</v>
+      </c>
+      <c r="H58">
+        <v>7.82</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K58">
+        <v>2.7</v>
+      </c>
+      <c r="L58">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M58">
+        <v>0.7825552000000001</v>
+      </c>
+      <c r="N58">
+        <v>2.384111466666667</v>
+      </c>
+      <c r="O58">
+        <v>0.429140064</v>
+      </c>
+      <c r="P58">
+        <v>1.954971402666667</v>
+      </c>
+      <c r="Q58">
+        <v>4.654971402666667</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1945636665071581</v>
+      </c>
+      <c r="T58">
+        <v>2.109288547421031</v>
+      </c>
+      <c r="U58">
+        <v>0.0535</v>
+      </c>
+      <c r="V58">
+        <v>0.18</v>
+      </c>
+      <c r="W58">
+        <v>0.04387</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>4.046572902035111</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1113506992864217</v>
+      </c>
+      <c r="C59">
+        <v>20.83458876670485</v>
+      </c>
+      <c r="D59">
+        <v>31.94298876670485</v>
+      </c>
+      <c r="E59">
+        <v>-3.411599999999998</v>
+      </c>
+      <c r="F59">
+        <v>14.8884</v>
+      </c>
+      <c r="G59">
+        <v>3.78</v>
+      </c>
+      <c r="H59">
+        <v>7.82</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K59">
+        <v>2.7</v>
+      </c>
+      <c r="L59">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M59">
+        <v>0.8367280800000001</v>
+      </c>
+      <c r="N59">
+        <v>2.329938586666667</v>
+      </c>
+      <c r="O59">
+        <v>0.4193889456</v>
+      </c>
+      <c r="P59">
+        <v>1.910549641066667</v>
+      </c>
+      <c r="Q59">
+        <v>4.610549641066667</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1978670215963295</v>
+      </c>
+      <c r="T59">
+        <v>2.154021245449388</v>
+      </c>
+      <c r="U59">
+        <v>0.0562</v>
+      </c>
+      <c r="V59">
+        <v>0.18</v>
+      </c>
+      <c r="W59">
+        <v>0.04608400000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.784582760347503</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1112863453096939</v>
+      </c>
+      <c r="C60">
+        <v>20.60174801625629</v>
+      </c>
+      <c r="D60">
+        <v>31.97134801625629</v>
+      </c>
+      <c r="E60">
+        <v>-3.150400000000001</v>
+      </c>
+      <c r="F60">
+        <v>15.1496</v>
+      </c>
+      <c r="G60">
+        <v>3.78</v>
+      </c>
+      <c r="H60">
+        <v>7.82</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K60">
+        <v>2.7</v>
+      </c>
+      <c r="L60">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M60">
+        <v>0.85140752</v>
+      </c>
+      <c r="N60">
+        <v>2.315259146666667</v>
+      </c>
+      <c r="O60">
+        <v>0.4167466464</v>
+      </c>
+      <c r="P60">
+        <v>1.898512500266667</v>
+      </c>
+      <c r="Q60">
+        <v>4.598512500266667</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2013276793087949</v>
+      </c>
+      <c r="T60">
+        <v>2.200884071955285</v>
+      </c>
+      <c r="U60">
+        <v>0.0562</v>
+      </c>
+      <c r="V60">
+        <v>0.18</v>
+      </c>
+      <c r="W60">
+        <v>0.04608400000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.719331333444961</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.111221991332966</v>
+      </c>
+      <c r="C61">
+        <v>20.36895766570568</v>
+      </c>
+      <c r="D61">
+        <v>31.99975766570568</v>
+      </c>
+      <c r="E61">
+        <v>-2.889200000000001</v>
+      </c>
+      <c r="F61">
+        <v>15.4108</v>
+      </c>
+      <c r="G61">
+        <v>3.78</v>
+      </c>
+      <c r="H61">
+        <v>7.82</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K61">
+        <v>2.7</v>
+      </c>
+      <c r="L61">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M61">
+        <v>0.86608696</v>
+      </c>
+      <c r="N61">
+        <v>2.300579706666667</v>
+      </c>
+      <c r="O61">
+        <v>0.4141043472</v>
+      </c>
+      <c r="P61">
+        <v>1.886475359466667</v>
+      </c>
+      <c r="Q61">
+        <v>4.586475359466667</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2049571495926</v>
+      </c>
+      <c r="T61">
+        <v>2.250032889998056</v>
+      </c>
+      <c r="U61">
+        <v>0.0562</v>
+      </c>
+      <c r="V61">
+        <v>0.18</v>
+      </c>
+      <c r="W61">
+        <v>0.04608400000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.656291819318775</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1111576373562382</v>
+      </c>
+      <c r="C62">
+        <v>20.13621784952811</v>
+      </c>
+      <c r="D62">
+        <v>32.0282178495281</v>
+      </c>
+      <c r="E62">
+        <v>-2.628</v>
+      </c>
+      <c r="F62">
+        <v>15.672</v>
+      </c>
+      <c r="G62">
+        <v>3.78</v>
+      </c>
+      <c r="H62">
+        <v>7.82</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K62">
+        <v>2.7</v>
+      </c>
+      <c r="L62">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M62">
+        <v>0.8807664000000001</v>
+      </c>
+      <c r="N62">
+        <v>2.285900266666667</v>
+      </c>
+      <c r="O62">
+        <v>0.411462048</v>
+      </c>
+      <c r="P62">
+        <v>1.874438218666667</v>
+      </c>
+      <c r="Q62">
+        <v>4.574438218666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2087680933905955</v>
+      </c>
+      <c r="T62">
+        <v>2.301639148942966</v>
+      </c>
+      <c r="U62">
+        <v>0.0562</v>
+      </c>
+      <c r="V62">
+        <v>0.18</v>
+      </c>
+      <c r="W62">
+        <v>0.04608400000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.595353622330128</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1110932833795104</v>
+      </c>
+      <c r="C63">
+        <v>19.90352870267753</v>
+      </c>
+      <c r="D63">
+        <v>32.05672870267753</v>
+      </c>
+      <c r="E63">
+        <v>-2.3668</v>
+      </c>
+      <c r="F63">
+        <v>15.9332</v>
+      </c>
+      <c r="G63">
+        <v>3.78</v>
+      </c>
+      <c r="H63">
+        <v>7.82</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K63">
+        <v>2.7</v>
+      </c>
+      <c r="L63">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M63">
+        <v>0.89544584</v>
+      </c>
+      <c r="N63">
+        <v>2.271220826666667</v>
+      </c>
+      <c r="O63">
+        <v>0.4088197488</v>
+      </c>
+      <c r="P63">
+        <v>1.862401077866667</v>
+      </c>
+      <c r="Q63">
+        <v>4.562401077866667</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2127744702038727</v>
+      </c>
+      <c r="T63">
+        <v>2.355891882705563</v>
+      </c>
+      <c r="U63">
+        <v>0.0562</v>
+      </c>
+      <c r="V63">
+        <v>0.18</v>
+      </c>
+      <c r="W63">
+        <v>0.04608400000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.536413399013241</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1134184094027825</v>
+      </c>
+      <c r="C64">
+        <v>18.64343399661065</v>
+      </c>
+      <c r="D64">
+        <v>31.05783399661065</v>
+      </c>
+      <c r="E64">
+        <v>-2.105599999999999</v>
+      </c>
+      <c r="F64">
+        <v>16.1944</v>
+      </c>
+      <c r="G64">
+        <v>3.78</v>
+      </c>
+      <c r="H64">
+        <v>7.82</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K64">
+        <v>2.7</v>
+      </c>
+      <c r="L64">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M64">
+        <v>0.9862389600000001</v>
+      </c>
+      <c r="N64">
+        <v>2.180427706666667</v>
+      </c>
+      <c r="O64">
+        <v>0.3924769872</v>
+      </c>
+      <c r="P64">
+        <v>1.787950719466667</v>
+      </c>
+      <c r="Q64">
+        <v>4.487950719466667</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2169917089546908</v>
+      </c>
+      <c r="T64">
+        <v>2.413000023508296</v>
+      </c>
+      <c r="U64">
+        <v>0.0609</v>
+      </c>
+      <c r="V64">
+        <v>0.18</v>
+      </c>
+      <c r="W64">
+        <v>0.049938</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.210851320116847</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1133925954260547</v>
+      </c>
+      <c r="C65">
+        <v>18.39298206348545</v>
+      </c>
+      <c r="D65">
+        <v>31.06858206348545</v>
+      </c>
+      <c r="E65">
+        <v>-1.8444</v>
+      </c>
+      <c r="F65">
+        <v>16.4556</v>
+      </c>
+      <c r="G65">
+        <v>3.78</v>
+      </c>
+      <c r="H65">
+        <v>7.82</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K65">
+        <v>2.7</v>
+      </c>
+      <c r="L65">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M65">
+        <v>1.00214604</v>
+      </c>
+      <c r="N65">
+        <v>2.164520626666667</v>
+      </c>
+      <c r="O65">
+        <v>0.3896137128</v>
+      </c>
+      <c r="P65">
+        <v>1.774906913866667</v>
+      </c>
+      <c r="Q65">
+        <v>4.474906913866667</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2214369065569046</v>
+      </c>
+      <c r="T65">
+        <v>2.473195090840909</v>
+      </c>
+      <c r="U65">
+        <v>0.0609</v>
+      </c>
+      <c r="V65">
+        <v>0.18</v>
+      </c>
+      <c r="W65">
+        <v>0.049938</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>3.159885426146738</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1133667814493269</v>
+      </c>
+      <c r="C66">
+        <v>18.14253757202109</v>
+      </c>
+      <c r="D66">
+        <v>31.07933757202109</v>
+      </c>
+      <c r="E66">
+        <v>-1.583200000000001</v>
+      </c>
+      <c r="F66">
+        <v>16.7168</v>
+      </c>
+      <c r="G66">
+        <v>3.78</v>
+      </c>
+      <c r="H66">
+        <v>7.82</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K66">
+        <v>2.7</v>
+      </c>
+      <c r="L66">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M66">
+        <v>1.01805312</v>
+      </c>
+      <c r="N66">
+        <v>2.148613546666667</v>
+      </c>
+      <c r="O66">
+        <v>0.3867504384</v>
+      </c>
+      <c r="P66">
+        <v>1.761863108266667</v>
+      </c>
+      <c r="Q66">
+        <v>4.461863108266667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2261290595814635</v>
+      </c>
+      <c r="T66">
+        <v>2.536734328580887</v>
+      </c>
+      <c r="U66">
+        <v>0.0609</v>
+      </c>
+      <c r="V66">
+        <v>0.18</v>
+      </c>
+      <c r="W66">
+        <v>0.049938</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>3.110512216363196</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.113340967472599</v>
+      </c>
+      <c r="C67">
+        <v>17.89210052994883</v>
+      </c>
+      <c r="D67">
+        <v>31.09010052994883</v>
+      </c>
+      <c r="E67">
+        <v>-1.321999999999999</v>
+      </c>
+      <c r="F67">
+        <v>16.978</v>
+      </c>
+      <c r="G67">
+        <v>3.78</v>
+      </c>
+      <c r="H67">
+        <v>7.82</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K67">
+        <v>2.7</v>
+      </c>
+      <c r="L67">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M67">
+        <v>1.0339602</v>
+      </c>
+      <c r="N67">
+        <v>2.132706466666667</v>
+      </c>
+      <c r="O67">
+        <v>0.383887164</v>
+      </c>
+      <c r="P67">
+        <v>1.748819302666667</v>
+      </c>
+      <c r="Q67">
+        <v>4.448819302666667</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2310893356359972</v>
+      </c>
+      <c r="T67">
+        <v>2.603904379906008</v>
+      </c>
+      <c r="U67">
+        <v>0.0609</v>
+      </c>
+      <c r="V67">
+        <v>0.18</v>
+      </c>
+      <c r="W67">
+        <v>0.049938</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>3.062658182265301</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1133151534958712</v>
+      </c>
+      <c r="C68">
+        <v>17.64167094501067</v>
+      </c>
+      <c r="D68">
+        <v>31.10087094501067</v>
+      </c>
+      <c r="E68">
+        <v>-1.0608</v>
+      </c>
+      <c r="F68">
+        <v>17.2392</v>
+      </c>
+      <c r="G68">
+        <v>3.78</v>
+      </c>
+      <c r="H68">
+        <v>7.82</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K68">
+        <v>2.7</v>
+      </c>
+      <c r="L68">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M68">
+        <v>1.04986728</v>
+      </c>
+      <c r="N68">
+        <v>2.116799386666667</v>
+      </c>
+      <c r="O68">
+        <v>0.3810238896000001</v>
+      </c>
+      <c r="P68">
+        <v>1.735775497066667</v>
+      </c>
+      <c r="Q68">
+        <v>4.435775497066667</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2363413926349152</v>
+      </c>
+      <c r="T68">
+        <v>2.675025610720841</v>
+      </c>
+      <c r="U68">
+        <v>0.0609</v>
+      </c>
+      <c r="V68">
+        <v>0.18</v>
+      </c>
+      <c r="W68">
+        <v>0.049938</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>3.016254270412797</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1183987595191434</v>
+      </c>
+      <c r="C69">
+        <v>15.39420161342587</v>
+      </c>
+      <c r="D69">
+        <v>29.11460161342588</v>
+      </c>
+      <c r="E69">
+        <v>-0.7995999999999981</v>
+      </c>
+      <c r="F69">
+        <v>17.5004</v>
+      </c>
+      <c r="G69">
+        <v>3.78</v>
+      </c>
+      <c r="H69">
+        <v>7.82</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K69">
+        <v>2.7</v>
+      </c>
+      <c r="L69">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M69">
+        <v>1.22852808</v>
+      </c>
+      <c r="N69">
+        <v>1.938138586666667</v>
+      </c>
+      <c r="O69">
+        <v>0.3488649456</v>
+      </c>
+      <c r="P69">
+        <v>1.589273641066667</v>
+      </c>
+      <c r="Q69">
+        <v>4.289273641066667</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2419117561186162</v>
+      </c>
+      <c r="T69">
+        <v>2.750457219160816</v>
+      </c>
+      <c r="U69">
+        <v>0.0702</v>
+      </c>
+      <c r="V69">
+        <v>0.18</v>
+      </c>
+      <c r="W69">
+        <v>0.057564</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.577610327528424</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1184492055424155</v>
+      </c>
+      <c r="C70">
+        <v>15.11456180777373</v>
+      </c>
+      <c r="D70">
+        <v>29.09616180777373</v>
+      </c>
+      <c r="E70">
+        <v>-0.5383999999999993</v>
+      </c>
+      <c r="F70">
+        <v>17.7616</v>
+      </c>
+      <c r="G70">
+        <v>3.78</v>
+      </c>
+      <c r="H70">
+        <v>7.82</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K70">
+        <v>2.7</v>
+      </c>
+      <c r="L70">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M70">
+        <v>1.24686432</v>
+      </c>
+      <c r="N70">
+        <v>1.919802346666667</v>
+      </c>
+      <c r="O70">
+        <v>0.3455644224</v>
+      </c>
+      <c r="P70">
+        <v>1.574237924266667</v>
+      </c>
+      <c r="Q70">
+        <v>4.274237924266667</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2478302673200485</v>
+      </c>
+      <c r="T70">
+        <v>2.830603303128289</v>
+      </c>
+      <c r="U70">
+        <v>0.0702</v>
+      </c>
+      <c r="V70">
+        <v>0.18</v>
+      </c>
+      <c r="W70">
+        <v>0.057564</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.539704293300066</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1184996515656877</v>
+      </c>
+      <c r="C71">
+        <v>14.83494534513115</v>
+      </c>
+      <c r="D71">
+        <v>29.07774534513115</v>
+      </c>
+      <c r="E71">
+        <v>-0.277199999999997</v>
+      </c>
+      <c r="F71">
+        <v>18.0228</v>
+      </c>
+      <c r="G71">
+        <v>3.78</v>
+      </c>
+      <c r="H71">
+        <v>7.82</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K71">
+        <v>2.7</v>
+      </c>
+      <c r="L71">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M71">
+        <v>1.26520056</v>
+      </c>
+      <c r="N71">
+        <v>1.901466106666667</v>
+      </c>
+      <c r="O71">
+        <v>0.3422638992</v>
+      </c>
+      <c r="P71">
+        <v>1.559202207466667</v>
+      </c>
+      <c r="Q71">
+        <v>4.259202207466667</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2541306179538313</v>
+      </c>
+      <c r="T71">
+        <v>2.915920102190438</v>
+      </c>
+      <c r="U71">
+        <v>0.0702</v>
+      </c>
+      <c r="V71">
+        <v>0.18</v>
+      </c>
+      <c r="W71">
+        <v>0.057564</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.502896984701513</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1212478975889598</v>
+      </c>
+      <c r="C72">
+        <v>13.60449324353266</v>
+      </c>
+      <c r="D72">
+        <v>28.10849324353266</v>
+      </c>
+      <c r="E72">
+        <v>-0.01599999999999824</v>
+      </c>
+      <c r="F72">
+        <v>18.284</v>
+      </c>
+      <c r="G72">
+        <v>3.78</v>
+      </c>
+      <c r="H72">
+        <v>7.82</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K72">
+        <v>2.7</v>
+      </c>
+      <c r="L72">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M72">
+        <v>1.3694716</v>
+      </c>
+      <c r="N72">
+        <v>1.797195066666667</v>
+      </c>
+      <c r="O72">
+        <v>0.323495112</v>
+      </c>
+      <c r="P72">
+        <v>1.473699954666667</v>
+      </c>
+      <c r="Q72">
+        <v>4.173699954666667</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2608509919631995</v>
+      </c>
+      <c r="T72">
+        <v>3.00692468785673</v>
+      </c>
+      <c r="U72">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V72">
+        <v>0.18</v>
+      </c>
+      <c r="W72">
+        <v>0.061418</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.312327372591492</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.121336883612232</v>
+      </c>
+      <c r="C73">
+        <v>13.31298845221456</v>
+      </c>
+      <c r="D73">
+        <v>28.07818845221456</v>
+      </c>
+      <c r="E73">
+        <v>0.2452000000000005</v>
+      </c>
+      <c r="F73">
+        <v>18.5452</v>
+      </c>
+      <c r="G73">
+        <v>3.78</v>
+      </c>
+      <c r="H73">
+        <v>7.82</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K73">
+        <v>2.7</v>
+      </c>
+      <c r="L73">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M73">
+        <v>1.38903548</v>
+      </c>
+      <c r="N73">
+        <v>1.777631186666667</v>
+      </c>
+      <c r="O73">
+        <v>0.3199736136</v>
+      </c>
+      <c r="P73">
+        <v>1.457657573066667</v>
+      </c>
+      <c r="Q73">
+        <v>4.157657573066667</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2680348400421794</v>
+      </c>
+      <c r="T73">
+        <v>3.104205451844835</v>
+      </c>
+      <c r="U73">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V73">
+        <v>0.18</v>
+      </c>
+      <c r="W73">
+        <v>0.061418</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.279759381428232</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1214258696355042</v>
+      </c>
+      <c r="C74">
+        <v>13.02154893592176</v>
+      </c>
+      <c r="D74">
+        <v>28.04794893592176</v>
+      </c>
+      <c r="E74">
+        <v>0.5063999999999993</v>
+      </c>
+      <c r="F74">
+        <v>18.8064</v>
+      </c>
+      <c r="G74">
+        <v>3.78</v>
+      </c>
+      <c r="H74">
+        <v>7.82</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K74">
+        <v>2.7</v>
+      </c>
+      <c r="L74">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M74">
+        <v>1.40859936</v>
+      </c>
+      <c r="N74">
+        <v>1.758067306666667</v>
+      </c>
+      <c r="O74">
+        <v>0.3164521152000001</v>
+      </c>
+      <c r="P74">
+        <v>1.441615191466667</v>
+      </c>
+      <c r="Q74">
+        <v>4.141615191466667</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2757318201268006</v>
+      </c>
+      <c r="T74">
+        <v>3.208434841832091</v>
+      </c>
+      <c r="U74">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V74">
+        <v>0.18</v>
+      </c>
+      <c r="W74">
+        <v>0.061418</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.248096056686173</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1215148556587763</v>
+      </c>
+      <c r="C75">
+        <v>12.73017448398239</v>
+      </c>
+      <c r="D75">
+        <v>28.01777448398239</v>
+      </c>
+      <c r="E75">
+        <v>0.7675999999999981</v>
+      </c>
+      <c r="F75">
+        <v>19.0676</v>
+      </c>
+      <c r="G75">
+        <v>3.78</v>
+      </c>
+      <c r="H75">
+        <v>7.82</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K75">
+        <v>2.7</v>
+      </c>
+      <c r="L75">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M75">
+        <v>1.42816324</v>
+      </c>
+      <c r="N75">
+        <v>1.738503426666667</v>
+      </c>
+      <c r="O75">
+        <v>0.3129306168000001</v>
+      </c>
+      <c r="P75">
+        <v>1.425572809866667</v>
+      </c>
+      <c r="Q75">
+        <v>4.125572809866667</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2839989468843568</v>
+      </c>
+      <c r="T75">
+        <v>3.320384927373958</v>
+      </c>
+      <c r="U75">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V75">
+        <v>0.18</v>
+      </c>
+      <c r="W75">
+        <v>0.061418</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.217300220293212</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1216038416820485</v>
+      </c>
+      <c r="C76">
+        <v>12.43886488663014</v>
+      </c>
+      <c r="D76">
+        <v>27.98766488663014</v>
+      </c>
+      <c r="E76">
+        <v>1.0288</v>
+      </c>
+      <c r="F76">
+        <v>19.3288</v>
+      </c>
+      <c r="G76">
+        <v>3.78</v>
+      </c>
+      <c r="H76">
+        <v>7.82</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K76">
+        <v>2.7</v>
+      </c>
+      <c r="L76">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M76">
+        <v>1.44772712</v>
+      </c>
+      <c r="N76">
+        <v>1.718939546666667</v>
+      </c>
+      <c r="O76">
+        <v>0.3094091184000001</v>
+      </c>
+      <c r="P76">
+        <v>1.409530428266667</v>
+      </c>
+      <c r="Q76">
+        <v>4.109530428266667</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2929020064694173</v>
+      </c>
+      <c r="T76">
+        <v>3.440946557957507</v>
+      </c>
+      <c r="U76">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V76">
+        <v>0.18</v>
+      </c>
+      <c r="W76">
+        <v>0.061418</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.187336703802763</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1216928277053207</v>
+      </c>
+      <c r="C77">
+        <v>12.14761993499948</v>
+      </c>
+      <c r="D77">
+        <v>27.95761993499947</v>
+      </c>
+      <c r="E77">
+        <v>1.289999999999999</v>
+      </c>
+      <c r="F77">
+        <v>19.59</v>
+      </c>
+      <c r="G77">
+        <v>3.78</v>
+      </c>
+      <c r="H77">
+        <v>7.82</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K77">
+        <v>2.7</v>
+      </c>
+      <c r="L77">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M77">
+        <v>1.467291</v>
+      </c>
+      <c r="N77">
+        <v>1.699375666666667</v>
+      </c>
+      <c r="O77">
+        <v>0.3058876200000001</v>
+      </c>
+      <c r="P77">
+        <v>1.393488046666667</v>
+      </c>
+      <c r="Q77">
+        <v>4.093488046666668</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3025173108212826</v>
+      </c>
+      <c r="T77">
+        <v>3.57115311898774</v>
+      </c>
+      <c r="U77">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V77">
+        <v>0.18</v>
+      </c>
+      <c r="W77">
+        <v>0.061418</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.158172214418726</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1217818137285928</v>
+      </c>
+      <c r="C78">
+        <v>11.85643942112077</v>
+      </c>
+      <c r="D78">
+        <v>27.92763942112077</v>
+      </c>
+      <c r="E78">
+        <v>1.551200000000001</v>
+      </c>
+      <c r="F78">
+        <v>19.8512</v>
+      </c>
+      <c r="G78">
+        <v>3.78</v>
+      </c>
+      <c r="H78">
+        <v>7.82</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K78">
+        <v>2.7</v>
+      </c>
+      <c r="L78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M78">
+        <v>1.48685488</v>
+      </c>
+      <c r="N78">
+        <v>1.679811786666667</v>
+      </c>
+      <c r="O78">
+        <v>0.3023661216</v>
+      </c>
+      <c r="P78">
+        <v>1.377445665066667</v>
+      </c>
+      <c r="Q78">
+        <v>4.077445665066668</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3129338905358035</v>
+      </c>
+      <c r="T78">
+        <v>3.712210226770494</v>
+      </c>
+      <c r="U78">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V78">
+        <v>0.18</v>
+      </c>
+      <c r="W78">
+        <v>0.061418</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.129775211597427</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.121870799751865</v>
+      </c>
+      <c r="C79">
+        <v>11.56532313791551</v>
+      </c>
+      <c r="D79">
+        <v>27.89772313791551</v>
+      </c>
+      <c r="E79">
+        <v>1.8124</v>
+      </c>
+      <c r="F79">
+        <v>20.1124</v>
+      </c>
+      <c r="G79">
+        <v>3.78</v>
+      </c>
+      <c r="H79">
+        <v>7.82</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K79">
+        <v>2.7</v>
+      </c>
+      <c r="L79">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M79">
+        <v>1.50641876</v>
+      </c>
+      <c r="N79">
+        <v>1.660247906666667</v>
+      </c>
+      <c r="O79">
+        <v>0.2988446232</v>
+      </c>
+      <c r="P79">
+        <v>1.361403283466667</v>
+      </c>
+      <c r="Q79">
+        <v>4.061403283466667</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3242562597907174</v>
+      </c>
+      <c r="T79">
+        <v>3.865533170012616</v>
+      </c>
+      <c r="U79">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V79">
+        <v>0.18</v>
+      </c>
+      <c r="W79">
+        <v>0.061418</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>2.102115793264993</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1219597857751372</v>
+      </c>
+      <c r="C80">
+        <v>11.27427087919152</v>
+      </c>
+      <c r="D80">
+        <v>27.86787087919152</v>
+      </c>
+      <c r="E80">
+        <v>2.073599999999999</v>
+      </c>
+      <c r="F80">
+        <v>20.3736</v>
+      </c>
+      <c r="G80">
+        <v>3.78</v>
+      </c>
+      <c r="H80">
+        <v>7.82</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K80">
+        <v>2.7</v>
+      </c>
+      <c r="L80">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M80">
+        <v>1.52598264</v>
+      </c>
+      <c r="N80">
+        <v>1.640684026666667</v>
+      </c>
+      <c r="O80">
+        <v>0.2953231248000001</v>
+      </c>
+      <c r="P80">
+        <v>1.345360901866667</v>
+      </c>
+      <c r="Q80">
+        <v>4.045360901866667</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3366079353415325</v>
+      </c>
+      <c r="T80">
+        <v>4.032794562640386</v>
+      </c>
+      <c r="U80">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V80">
+        <v>0.18</v>
+      </c>
+      <c r="W80">
+        <v>0.061418</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>2.075165590787237</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1220487717984093</v>
+      </c>
+      <c r="C81">
+        <v>10.98328243963824</v>
+      </c>
+      <c r="D81">
+        <v>27.83808243963824</v>
+      </c>
+      <c r="E81">
+        <v>2.334800000000001</v>
+      </c>
+      <c r="F81">
+        <v>20.6348</v>
+      </c>
+      <c r="G81">
+        <v>3.78</v>
+      </c>
+      <c r="H81">
+        <v>7.82</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K81">
+        <v>2.7</v>
+      </c>
+      <c r="L81">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M81">
+        <v>1.54554652</v>
+      </c>
+      <c r="N81">
+        <v>1.621120146666667</v>
+      </c>
+      <c r="O81">
+        <v>0.2918016264</v>
+      </c>
+      <c r="P81">
+        <v>1.329318520266667</v>
+      </c>
+      <c r="Q81">
+        <v>4.029318520266667</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3501359609448064</v>
+      </c>
+      <c r="T81">
+        <v>4.215985611708897</v>
+      </c>
+      <c r="U81">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V81">
+        <v>0.18</v>
+      </c>
+      <c r="W81">
+        <v>0.061418</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.048897671916512</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1221377578216815</v>
+      </c>
+      <c r="C82">
+        <v>10.69235761482203</v>
+      </c>
+      <c r="D82">
+        <v>27.80835761482203</v>
+      </c>
+      <c r="E82">
+        <v>2.596</v>
+      </c>
+      <c r="F82">
+        <v>20.896</v>
+      </c>
+      <c r="G82">
+        <v>3.78</v>
+      </c>
+      <c r="H82">
+        <v>7.82</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K82">
+        <v>2.7</v>
+      </c>
+      <c r="L82">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M82">
+        <v>1.5651104</v>
+      </c>
+      <c r="N82">
+        <v>1.601556266666667</v>
+      </c>
+      <c r="O82">
+        <v>0.288280128</v>
+      </c>
+      <c r="P82">
+        <v>1.313276138666667</v>
+      </c>
+      <c r="Q82">
+        <v>4.013276138666667</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3650167891084075</v>
+      </c>
+      <c r="T82">
+        <v>4.417495765684258</v>
+      </c>
+      <c r="U82">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V82">
+        <v>0.18</v>
+      </c>
+      <c r="W82">
+        <v>0.061418</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.023286451017555</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1330532038449537</v>
+      </c>
+      <c r="C83">
+        <v>7.210676886763547</v>
+      </c>
+      <c r="D83">
+        <v>24.58787688676355</v>
+      </c>
+      <c r="E83">
+        <v>2.857200000000002</v>
+      </c>
+      <c r="F83">
+        <v>21.1572</v>
+      </c>
+      <c r="G83">
+        <v>3.78</v>
+      </c>
+      <c r="H83">
+        <v>7.82</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K83">
+        <v>2.7</v>
+      </c>
+      <c r="L83">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M83">
+        <v>1.92953664</v>
+      </c>
+      <c r="N83">
+        <v>1.237130026666667</v>
+      </c>
+      <c r="O83">
+        <v>0.2226834048</v>
+      </c>
+      <c r="P83">
+        <v>1.014446621866667</v>
+      </c>
+      <c r="Q83">
+        <v>3.714446621866667</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3814640202365983</v>
+      </c>
+      <c r="T83">
+        <v>4.640217514814921</v>
+      </c>
+      <c r="U83">
+        <v>0.0912</v>
+      </c>
+      <c r="V83">
+        <v>0.18</v>
+      </c>
+      <c r="W83">
+        <v>0.074784</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>1.641153943916124</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1332758498682258</v>
+      </c>
+      <c r="C84">
+        <v>6.891531993786366</v>
+      </c>
+      <c r="D84">
+        <v>24.52993199378637</v>
+      </c>
+      <c r="E84">
+        <v>3.118400000000001</v>
+      </c>
+      <c r="F84">
+        <v>21.4184</v>
+      </c>
+      <c r="G84">
+        <v>3.78</v>
+      </c>
+      <c r="H84">
+        <v>7.82</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K84">
+        <v>2.7</v>
+      </c>
+      <c r="L84">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M84">
+        <v>1.95335808</v>
+      </c>
+      <c r="N84">
+        <v>1.213308586666667</v>
+      </c>
+      <c r="O84">
+        <v>0.2183955456</v>
+      </c>
+      <c r="P84">
+        <v>0.9949130410666667</v>
+      </c>
+      <c r="Q84">
+        <v>3.694913041066667</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3997387214901435</v>
+      </c>
+      <c r="T84">
+        <v>4.8876861249601</v>
+      </c>
+      <c r="U84">
+        <v>0.0912</v>
+      </c>
+      <c r="V84">
+        <v>0.18</v>
+      </c>
+      <c r="W84">
+        <v>0.074784</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>1.621139871429342</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.133498495891498</v>
+      </c>
+      <c r="C85">
+        <v>6.57265956976169</v>
+      </c>
+      <c r="D85">
+        <v>24.47225956976169</v>
+      </c>
+      <c r="E85">
+        <v>3.379600000000003</v>
+      </c>
+      <c r="F85">
+        <v>21.6796</v>
+      </c>
+      <c r="G85">
+        <v>3.78</v>
+      </c>
+      <c r="H85">
+        <v>7.82</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K85">
+        <v>2.7</v>
+      </c>
+      <c r="L85">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M85">
+        <v>1.97717952</v>
+      </c>
+      <c r="N85">
+        <v>1.189487146666667</v>
+      </c>
+      <c r="O85">
+        <v>0.2141076864</v>
+      </c>
+      <c r="P85">
+        <v>0.9753794602666666</v>
+      </c>
+      <c r="Q85">
+        <v>3.675379460266667</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4201633875970471</v>
+      </c>
+      <c r="T85">
+        <v>5.164268689240009</v>
+      </c>
+      <c r="U85">
+        <v>0.0912</v>
+      </c>
+      <c r="V85">
+        <v>0.18</v>
+      </c>
+      <c r="W85">
+        <v>0.074784</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.60160806574947</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1337211419147701</v>
+      </c>
+      <c r="C86">
+        <v>6.254057697388692</v>
+      </c>
+      <c r="D86">
+        <v>24.41485769738869</v>
+      </c>
+      <c r="E86">
+        <v>3.640799999999999</v>
+      </c>
+      <c r="F86">
+        <v>21.9408</v>
+      </c>
+      <c r="G86">
+        <v>3.78</v>
+      </c>
+      <c r="H86">
+        <v>7.82</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K86">
+        <v>2.7</v>
+      </c>
+      <c r="L86">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M86">
+        <v>2.00100096</v>
+      </c>
+      <c r="N86">
+        <v>1.165665706666667</v>
+      </c>
+      <c r="O86">
+        <v>0.2098198272000001</v>
+      </c>
+      <c r="P86">
+        <v>0.9558458794666671</v>
+      </c>
+      <c r="Q86">
+        <v>3.655845879466667</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4431411369673134</v>
+      </c>
+      <c r="T86">
+        <v>5.475424074054902</v>
+      </c>
+      <c r="U86">
+        <v>0.0912</v>
+      </c>
+      <c r="V86">
+        <v>0.18</v>
+      </c>
+      <c r="W86">
+        <v>0.074784</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.582541303061977</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1339437879380423</v>
+      </c>
+      <c r="C87">
+        <v>5.935724477313194</v>
+      </c>
+      <c r="D87">
+        <v>24.35772447731319</v>
+      </c>
+      <c r="E87">
+        <v>3.902000000000001</v>
+      </c>
+      <c r="F87">
+        <v>22.202</v>
+      </c>
+      <c r="G87">
+        <v>3.78</v>
+      </c>
+      <c r="H87">
+        <v>7.82</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K87">
+        <v>2.7</v>
+      </c>
+      <c r="L87">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M87">
+        <v>2.0248224</v>
+      </c>
+      <c r="N87">
+        <v>1.141844266666667</v>
+      </c>
+      <c r="O87">
+        <v>0.205531968</v>
+      </c>
+      <c r="P87">
+        <v>0.9363122986666668</v>
+      </c>
+      <c r="Q87">
+        <v>3.636312298666667</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4691825862536155</v>
+      </c>
+      <c r="T87">
+        <v>5.828066843511785</v>
+      </c>
+      <c r="U87">
+        <v>0.0912</v>
+      </c>
+      <c r="V87">
+        <v>0.18</v>
+      </c>
+      <c r="W87">
+        <v>0.074784</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>1.563923170084777</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1341664339613145</v>
+      </c>
+      <c r="C88">
+        <v>5.617658027918303</v>
+      </c>
+      <c r="D88">
+        <v>24.3008580279183</v>
+      </c>
+      <c r="E88">
+        <v>4.1632</v>
+      </c>
+      <c r="F88">
+        <v>22.4632</v>
+      </c>
+      <c r="G88">
+        <v>3.78</v>
+      </c>
+      <c r="H88">
+        <v>7.82</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K88">
+        <v>2.7</v>
+      </c>
+      <c r="L88">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M88">
+        <v>2.04864384</v>
+      </c>
+      <c r="N88">
+        <v>1.118022826666667</v>
+      </c>
+      <c r="O88">
+        <v>0.2012441088</v>
+      </c>
+      <c r="P88">
+        <v>0.9167787178666669</v>
+      </c>
+      <c r="Q88">
+        <v>3.616778717866667</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4989442425808178</v>
+      </c>
+      <c r="T88">
+        <v>6.231087151462507</v>
+      </c>
+      <c r="U88">
+        <v>0.0912</v>
+      </c>
+      <c r="V88">
+        <v>0.18</v>
+      </c>
+      <c r="W88">
+        <v>0.074784</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>1.545738016944257</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1343890799845867</v>
+      </c>
+      <c r="C89">
+        <v>5.299856485117704</v>
+      </c>
+      <c r="D89">
+        <v>24.2442564851177</v>
+      </c>
+      <c r="E89">
+        <v>4.424399999999999</v>
+      </c>
+      <c r="F89">
+        <v>22.7244</v>
+      </c>
+      <c r="G89">
+        <v>3.78</v>
+      </c>
+      <c r="H89">
+        <v>7.82</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K89">
+        <v>2.7</v>
+      </c>
+      <c r="L89">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M89">
+        <v>2.07246528</v>
+      </c>
+      <c r="N89">
+        <v>1.094201386666667</v>
+      </c>
+      <c r="O89">
+        <v>0.1969562496000001</v>
+      </c>
+      <c r="P89">
+        <v>0.897245137066667</v>
+      </c>
+      <c r="Q89">
+        <v>3.597245137066667</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5332846152660511</v>
+      </c>
+      <c r="T89">
+        <v>6.69611058371334</v>
+      </c>
+      <c r="U89">
+        <v>0.0912</v>
+      </c>
+      <c r="V89">
+        <v>0.18</v>
+      </c>
+      <c r="W89">
+        <v>0.074784</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>1.527970913301219</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1346117260078588</v>
+      </c>
+      <c r="C90">
+        <v>4.98231800215207</v>
+      </c>
+      <c r="D90">
+        <v>24.18791800215207</v>
+      </c>
+      <c r="E90">
+        <v>4.685600000000001</v>
+      </c>
+      <c r="F90">
+        <v>22.9856</v>
+      </c>
+      <c r="G90">
+        <v>3.78</v>
+      </c>
+      <c r="H90">
+        <v>7.82</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K90">
+        <v>2.7</v>
+      </c>
+      <c r="L90">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M90">
+        <v>2.09628672</v>
+      </c>
+      <c r="N90">
+        <v>1.070379946666667</v>
+      </c>
+      <c r="O90">
+        <v>0.1926683904</v>
+      </c>
+      <c r="P90">
+        <v>0.8777115562666667</v>
+      </c>
+      <c r="Q90">
+        <v>3.577711556266667</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5733483833988235</v>
+      </c>
+      <c r="T90">
+        <v>7.238637921339313</v>
+      </c>
+      <c r="U90">
+        <v>0.0912</v>
+      </c>
+      <c r="V90">
+        <v>0.18</v>
+      </c>
+      <c r="W90">
+        <v>0.074784</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>1.510607607468251</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.187417345047187</v>
+      </c>
+      <c r="C91">
+        <v>-3.873154644628244</v>
+      </c>
+      <c r="D91">
+        <v>15.59364535537176</v>
+      </c>
+      <c r="E91">
+        <v>4.9468</v>
+      </c>
+      <c r="F91">
+        <v>23.2468</v>
+      </c>
+      <c r="G91">
+        <v>3.78</v>
+      </c>
+      <c r="H91">
+        <v>7.82</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K91">
+        <v>2.7</v>
+      </c>
+      <c r="L91">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M91">
+        <v>3.640448880000001</v>
+      </c>
+      <c r="N91">
+        <v>-0.4737822133333336</v>
+      </c>
+      <c r="O91">
+        <v>-0.08528079840000004</v>
+      </c>
+      <c r="P91">
+        <v>-0.3885014149333336</v>
+      </c>
+      <c r="Q91">
+        <v>2.311498585066667</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6351427581207454</v>
+      </c>
+      <c r="T91">
+        <v>8.075432340851796</v>
+      </c>
+      <c r="U91">
+        <v>0.1566</v>
+      </c>
+      <c r="V91">
+        <v>0.1565740980821024</v>
+      </c>
+      <c r="W91">
+        <v>0.1320804962403428</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.8698561004561247</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.188595345047187</v>
+      </c>
+      <c r="C92">
+        <v>-4.256984050921485</v>
+      </c>
+      <c r="D92">
+        <v>15.47101594907852</v>
+      </c>
+      <c r="E92">
+        <v>5.208000000000002</v>
+      </c>
+      <c r="F92">
+        <v>23.508</v>
+      </c>
+      <c r="G92">
+        <v>3.78</v>
+      </c>
+      <c r="H92">
+        <v>7.82</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K92">
+        <v>2.7</v>
+      </c>
+      <c r="L92">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M92">
+        <v>3.681352800000001</v>
+      </c>
+      <c r="N92">
+        <v>-0.5146861333333339</v>
+      </c>
+      <c r="O92">
+        <v>-0.0926435040000001</v>
+      </c>
+      <c r="P92">
+        <v>-0.4220426293333338</v>
+      </c>
+      <c r="Q92">
+        <v>2.277957370666666</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6947770339328199</v>
+      </c>
+      <c r="T92">
+        <v>8.882975574936976</v>
+      </c>
+      <c r="U92">
+        <v>0.1566</v>
+      </c>
+      <c r="V92">
+        <v>0.1548343858811902</v>
+      </c>
+      <c r="W92">
+        <v>0.1323529351710056</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.8601910326732788</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1897733450471871</v>
+      </c>
+      <c r="C93">
+        <v>-4.638899775821926</v>
+      </c>
+      <c r="D93">
+        <v>15.35030022417808</v>
+      </c>
+      <c r="E93">
+        <v>5.469200000000001</v>
+      </c>
+      <c r="F93">
+        <v>23.7692</v>
+      </c>
+      <c r="G93">
+        <v>3.78</v>
+      </c>
+      <c r="H93">
+        <v>7.82</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K93">
+        <v>2.7</v>
+      </c>
+      <c r="L93">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M93">
+        <v>3.722256720000001</v>
+      </c>
+      <c r="N93">
+        <v>-0.5555900533333338</v>
+      </c>
+      <c r="O93">
+        <v>-0.1000062096000001</v>
+      </c>
+      <c r="P93">
+        <v>-0.4555838437333337</v>
+      </c>
+      <c r="Q93">
+        <v>2.244416156266666</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7676633710364669</v>
+      </c>
+      <c r="T93">
+        <v>9.869972861041088</v>
+      </c>
+      <c r="U93">
+        <v>0.1566</v>
+      </c>
+      <c r="V93">
+        <v>0.153132909113265</v>
+      </c>
+      <c r="W93">
+        <v>0.1326193864328627</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.8507383839625834</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1909513450471871</v>
+      </c>
+      <c r="C94">
+        <v>-5.018946268164619</v>
+      </c>
+      <c r="D94">
+        <v>15.23145373183538</v>
+      </c>
+      <c r="E94">
+        <v>5.730399999999999</v>
+      </c>
+      <c r="F94">
+        <v>24.0304</v>
+      </c>
+      <c r="G94">
+        <v>3.78</v>
+      </c>
+      <c r="H94">
+        <v>7.82</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K94">
+        <v>2.7</v>
+      </c>
+      <c r="L94">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M94">
+        <v>3.763160640000001</v>
+      </c>
+      <c r="N94">
+        <v>-0.5964939733333336</v>
+      </c>
+      <c r="O94">
+        <v>-0.1073689152000001</v>
+      </c>
+      <c r="P94">
+        <v>-0.4891250581333336</v>
+      </c>
+      <c r="Q94">
+        <v>2.210874941866666</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8587712924160251</v>
+      </c>
+      <c r="T94">
+        <v>11.10371946867122</v>
+      </c>
+      <c r="U94">
+        <v>0.1566</v>
+      </c>
+      <c r="V94">
+        <v>0.1514684209707295</v>
+      </c>
+      <c r="W94">
+        <v>0.1328800452759838</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.841491227615164</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.192129345047187</v>
+      </c>
+      <c r="C95">
+        <v>-5.397166610817099</v>
+      </c>
+      <c r="D95">
+        <v>15.1144333891829</v>
+      </c>
+      <c r="E95">
+        <v>5.991600000000002</v>
+      </c>
+      <c r="F95">
+        <v>24.2916</v>
+      </c>
+      <c r="G95">
+        <v>3.78</v>
+      </c>
+      <c r="H95">
+        <v>7.82</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K95">
+        <v>2.7</v>
+      </c>
+      <c r="L95">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M95">
+        <v>3.804064560000001</v>
+      </c>
+      <c r="N95">
+        <v>-0.637397893333334</v>
+      </c>
+      <c r="O95">
+        <v>-0.1147316208000001</v>
+      </c>
+      <c r="P95">
+        <v>-0.5226662725333339</v>
+      </c>
+      <c r="Q95">
+        <v>2.177333727466666</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9759100484754575</v>
+      </c>
+      <c r="T95">
+        <v>12.68996510705283</v>
+      </c>
+      <c r="U95">
+        <v>0.1566</v>
+      </c>
+      <c r="V95">
+        <v>0.1498397282721195</v>
+      </c>
+      <c r="W95">
+        <v>0.1331350985525861</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.8324429348451085</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.193307345047187</v>
+      </c>
+      <c r="C96">
+        <v>-5.773602572751589</v>
+      </c>
+      <c r="D96">
+        <v>14.99919742724841</v>
+      </c>
+      <c r="E96">
+        <v>6.252800000000001</v>
+      </c>
+      <c r="F96">
+        <v>24.5528</v>
+      </c>
+      <c r="G96">
+        <v>3.78</v>
+      </c>
+      <c r="H96">
+        <v>7.82</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K96">
+        <v>2.7</v>
+      </c>
+      <c r="L96">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M96">
+        <v>3.844968480000001</v>
+      </c>
+      <c r="N96">
+        <v>-0.6783018133333338</v>
+      </c>
+      <c r="O96">
+        <v>-0.1220943264000001</v>
+      </c>
+      <c r="P96">
+        <v>-0.5562074869333338</v>
+      </c>
+      <c r="Q96">
+        <v>2.143792513066666</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.132095056554701</v>
+      </c>
+      <c r="T96">
+        <v>14.80495929156164</v>
+      </c>
+      <c r="U96">
+        <v>0.1566</v>
+      </c>
+      <c r="V96">
+        <v>0.1482456886096502</v>
+      </c>
+      <c r="W96">
+        <v>0.1333847251637288</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.823587158942501</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1944853450471871</v>
+      </c>
+      <c r="C97">
+        <v>-6.14829465875329</v>
+      </c>
+      <c r="D97">
+        <v>14.88570534124671</v>
+      </c>
+      <c r="E97">
+        <v>6.514000000000003</v>
+      </c>
+      <c r="F97">
+        <v>24.814</v>
+      </c>
+      <c r="G97">
+        <v>3.78</v>
+      </c>
+      <c r="H97">
+        <v>7.82</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K97">
+        <v>2.7</v>
+      </c>
+      <c r="L97">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M97">
+        <v>3.885872400000001</v>
+      </c>
+      <c r="N97">
+        <v>-0.7192057333333342</v>
+      </c>
+      <c r="O97">
+        <v>-0.1294570320000001</v>
+      </c>
+      <c r="P97">
+        <v>-0.589748701333334</v>
+      </c>
+      <c r="Q97">
+        <v>2.110251298666666</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.350754067865641</v>
+      </c>
+      <c r="T97">
+        <v>17.76595114987397</v>
+      </c>
+      <c r="U97">
+        <v>0.1566</v>
+      </c>
+      <c r="V97">
+        <v>0.146685207676917</v>
+      </c>
+      <c r="W97">
+        <v>0.1336290964777948</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8149178204273166</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.195663345047187</v>
+      </c>
+      <c r="C98">
+        <v>-6.521282156888773</v>
+      </c>
+      <c r="D98">
+        <v>14.77391784311123</v>
+      </c>
+      <c r="E98">
+        <v>6.775199999999998</v>
+      </c>
+      <c r="F98">
+        <v>25.0752</v>
+      </c>
+      <c r="G98">
+        <v>3.78</v>
+      </c>
+      <c r="H98">
+        <v>7.82</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K98">
+        <v>2.7</v>
+      </c>
+      <c r="L98">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M98">
+        <v>3.92677632</v>
+      </c>
+      <c r="N98">
+        <v>-0.7601096533333331</v>
+      </c>
+      <c r="O98">
+        <v>-0.1368197376</v>
+      </c>
+      <c r="P98">
+        <v>-0.6232899157333331</v>
+      </c>
+      <c r="Q98">
+        <v>2.076710084266667</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.678742584832048</v>
+      </c>
+      <c r="T98">
+        <v>22.20743893734242</v>
+      </c>
+      <c r="U98">
+        <v>0.1566</v>
+      </c>
+      <c r="V98">
+        <v>0.1451572367636158</v>
+      </c>
+      <c r="W98">
+        <v>0.1338683767228178</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.806429093131199</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2501306381888436</v>
+      </c>
+      <c r="C99">
+        <v>-10.59023725055588</v>
+      </c>
+      <c r="D99">
+        <v>10.96616274944412</v>
+      </c>
+      <c r="E99">
+        <v>7.0364</v>
+      </c>
+      <c r="F99">
+        <v>25.3364</v>
+      </c>
+      <c r="G99">
+        <v>3.78</v>
+      </c>
+      <c r="H99">
+        <v>7.82</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K99">
+        <v>2.7</v>
+      </c>
+      <c r="L99">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M99">
+        <v>5.290240320000001</v>
+      </c>
+      <c r="N99">
+        <v>-2.123573653333334</v>
+      </c>
+      <c r="O99">
+        <v>-0.3822432576000001</v>
+      </c>
+      <c r="P99">
+        <v>-1.741330395733333</v>
+      </c>
+      <c r="Q99">
+        <v>0.9586696042666667</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.31389988449795</v>
+      </c>
+      <c r="T99">
+        <v>30.80848209482733</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.107745577803921</v>
+      </c>
+      <c r="W99">
+        <v>0.1863027233545413</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5985865433551167</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2518306381888436</v>
+      </c>
+      <c r="C100">
+        <v>-10.93894802756219</v>
+      </c>
+      <c r="D100">
+        <v>10.87865197243782</v>
+      </c>
+      <c r="E100">
+        <v>7.297599999999999</v>
+      </c>
+      <c r="F100">
+        <v>25.5976</v>
+      </c>
+      <c r="G100">
+        <v>3.78</v>
+      </c>
+      <c r="H100">
+        <v>7.82</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K100">
+        <v>2.7</v>
+      </c>
+      <c r="L100">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M100">
+        <v>5.344778880000001</v>
+      </c>
+      <c r="N100">
+        <v>-2.178112213333334</v>
+      </c>
+      <c r="O100">
+        <v>-0.3920601984000001</v>
+      </c>
+      <c r="P100">
+        <v>-1.786052014933334</v>
+      </c>
+      <c r="Q100">
+        <v>0.9139479850666665</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.451449826746925</v>
+      </c>
+      <c r="T100">
+        <v>46.212723142241</v>
+      </c>
+      <c r="U100">
+        <v>0.2088</v>
+      </c>
+      <c r="V100">
+        <v>0.1066461331324524</v>
+      </c>
+      <c r="W100">
+        <v>0.1865322874019439</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5924785174025136</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2535306381888436</v>
+      </c>
+      <c r="C101">
+        <v>-11.28627317723403</v>
+      </c>
+      <c r="D101">
+        <v>10.79252682276597</v>
+      </c>
+      <c r="E101">
+        <v>7.558800000000002</v>
+      </c>
+      <c r="F101">
+        <v>25.8588</v>
+      </c>
+      <c r="G101">
+        <v>3.78</v>
+      </c>
+      <c r="H101">
+        <v>7.82</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>5.866666666666667</v>
+      </c>
+      <c r="K101">
+        <v>2.7</v>
+      </c>
+      <c r="L101">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="M101">
+        <v>5.399317440000001</v>
+      </c>
+      <c r="N101">
+        <v>-2.232650773333334</v>
+      </c>
+      <c r="O101">
+        <v>-0.4018771392000001</v>
+      </c>
+      <c r="P101">
+        <v>-1.830773634133334</v>
+      </c>
+      <c r="Q101">
+        <v>0.8692263658666664</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.86409965349385</v>
+      </c>
+      <c r="T101">
+        <v>92.42544628448201</v>
+      </c>
+      <c r="U101">
+        <v>0.2088</v>
+      </c>
+      <c r="V101">
+        <v>0.1055688994644478</v>
+      </c>
+      <c r="W101">
+        <v>0.1867572137918233</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.5864938859135992</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
